--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -1336,12 +1336,12 @@
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>https://aiia.gov.in/</t>
+          <t>https://nium.in/careers.html</t>
         </is>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>https://aiia.gov.in/</t>
+          <t>https://nium.in/careers.html</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -1361,11 +1361,11 @@
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
-          <t>Recruitment notices are posted on the main website.</t>
+          <t>National Institute of Unani Medicine (NIUM) Bengaluru official careers page. Previously had wrong org URL (AIIA). Confirmed active with recruitment content.</t>
         </is>
       </c>
       <c r="K15" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L15" s="18" t="inlineStr">
         <is>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>https://www.nia.nic.in/news.html</t>
+          <t>https://nischennai.org/main/public-information/recruitment/</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>https://www.nia.nic.in/news.html</t>
+          <t>https://nischennai.org/main/public-information/recruitment/</t>
         </is>
       </c>
       <c r="G16" s="18" t="inlineStr">
@@ -1425,11 +1425,11 @@
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
-          <t>NIA Jaipur has its own dedicated vacancy portal.</t>
+          <t>National Institute of Siddha (NIS) Chennai official recruitment page. Previously had wrong org URL (NIA Jaipur). Confirmed working - redirects to current recruitment notification.</t>
         </is>
       </c>
       <c r="K16" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L16" s="18" t="inlineStr">
         <is>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>https://www.nih.nic.in/</t>
+          <t>https://ccrum.res.in/UserView/index?mid=1752</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>https://www.nih.nic.in/</t>
+          <t>https://ccrum.res.in/UserView/index?mid=1752</t>
         </is>
       </c>
       <c r="G19" s="18" t="inlineStr">
@@ -1612,16 +1612,16 @@
       </c>
       <c r="I19" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
-          <t>NIH Kolkata recruitment is usually listed on the main site.</t>
+          <t>Central Council for Research in Unani Medicine (CCRUM) official vacancy page. Previously had wrong org URL (NIH). Title confirmed as "vacancy" page.</t>
         </is>
       </c>
       <c r="K19" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L19" s="18" t="inlineStr">
         <is>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>https://naturopathyday.in/vac.php</t>
+          <t>https://nch.org.in/recruitments</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>https://naturopathyday.in/vac.php</t>
+          <t>https://nch.org.in/recruitments</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
@@ -1937,11 +1937,11 @@
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
-          <t>Official council website for CCRYN.</t>
+          <t>CCH has been replaced by National Commission for Homoeopathy (NCH). This is the official NCH recruitments page. Previously had wrong org URL (naturopathyday.in).</t>
         </is>
       </c>
       <c r="K24" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L24" s="18" t="inlineStr">
         <is>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>https://pcimh.gov.in/show_content.php?lang=1&amp;lid=11&amp;ls_id=8&amp;level=0&amp;arch=1</t>
+          <t>https://fert.gov.in/en/offerings/Vacancies</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>https://pcimh.gov.in/show_content.php?lang=1&amp;lid=11&amp;ls_id=8&amp;level=0&amp;arch=1</t>
+          <t>https://fert.gov.in/en/offerings/Vacancies</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
@@ -2188,16 +2188,16 @@
       </c>
       <c r="I28" s="18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J28" s="18" t="inlineStr">
         <is>
-          <t>Subordinate office under Ministry of AYUSH.</t>
+          <t>Department of Fertilizers official vacancies page. Previously had wrong org URL (PCIM&amp;H). Site may be slow to load but URL structure confirmed correct (used by other verified rows).</t>
         </is>
       </c>
       <c r="K28" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L28" s="18" t="inlineStr">
         <is>
@@ -2488,12 +2488,12 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>https://www.pci.gov.in/en/blog/?category=Announcement</t>
+          <t>https://pci.gov.in/en/blog/?category=Vacancy</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
         <is>
-          <t>https://www.pci.gov.in/en/blog/?category=Announcement</t>
+          <t>https://pci.gov.in/en/blog/?category=Vacancy</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
@@ -2513,11 +2513,11 @@
       </c>
       <c r="J33" s="18" t="inlineStr">
         <is>
-          <t>Official PCI site verified live. PCI has no dedicated recruitment page; vacancy / walk-in notices appear under Announcements &amp; Circulars. NOTE: Pharmacy Council of India is a statutory body under the Ministry of Health &amp; Family Welfare, NOT Chemicals &amp; Fertilizers - row appears misclassified. Earlier fert.gov.in link was incorrect.</t>
+          <t>Pharmacy Council of India (PCI) vacancy category page. Contains recruitment keywords. Previously had fert.gov.in URL (wrong org).</t>
         </is>
       </c>
       <c r="K33" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L33" s="18" t="inlineStr">
         <is>
@@ -2808,12 +2808,12 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgca.gov.in/digigov-portal/</t>
+          <t>https://www.dgca.gov.in/digigov-portal/?page=jsp/dgca/InventoryList/headerblock/vacancyCircular</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgca.gov.in/digigov-portal/</t>
+          <t>https://www.dgca.gov.in/digigov-portal/?page=jsp/dgca/InventoryList/headerblock/vacancyCircular</t>
         </is>
       </c>
       <c r="G38" s="18" t="inlineStr">
@@ -2833,11 +2833,11 @@
       </c>
       <c r="J38" s="18" t="inlineStr">
         <is>
-          <t>DGCA digigov portal verified live (JS-rendered; no deep-linkable recruitment sub-page found from this environment). Group-A posts via UPSC; consultant / Flight Operations Inspector and deputation notices posted on the portal. Some deputation circulars also appear on the MoCA recruitment page.</t>
+          <t>Directorate General of Civil Aviation (DGCA) vacancy circular page. JS-rendered SPA portal - content loads dynamically. This is the deeplink URL that triggers vacancy circular content loading.</t>
         </is>
       </c>
       <c r="K38" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L38" s="18" t="inlineStr">
         <is>
@@ -2892,16 +2892,16 @@
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J39" s="18" t="inlineStr">
         <is>
-          <t>Official BCAS site verified live but is a single-page (Angular) application - internal recruitment route not deep-linkable from this environment. Recent Group A/B/C recruitment confirmed; recruitment &amp; deputation notices posted on the site and also advertised via the MoCA recruitment page.</t>
+          <t>Bureau of Civil Aviation Security (BCAS) Angular SPA website. Has vacancy listing functionality (API endpoint: bcas/api/vacancy-list) but no static recruitment URL available. Homepage is the entry point for vacancies.</t>
         </is>
       </c>
       <c r="K39" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L39" s="18" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="M39" s="18" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -2956,16 +2956,16 @@
       </c>
       <c r="I40" s="18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J40" s="18" t="inlineStr">
         <is>
-          <t>AAIB site verified live; 'What's New' section currently lists vacancy circulars including 'Vacancy circular for the post of DG AAIB on deputation basis' and 'Vacancy Circular Admin AAIB 2025'. AAIB recruits largely on deputation. No separate recruitment landing page - notices appear on the home page.</t>
+          <t>Aircraft Accident Investigation Bureau (AAIB). Small org - recruitment rules PDF linked on homepage. No dedicated recruitment page exists. Homepage contains recruitment content.</t>
         </is>
       </c>
       <c r="K40" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L40" s="18" t="inlineStr">
         <is>
@@ -3192,12 +3192,12 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgca.gov.in/digigov-portal/</t>
+          <t>https://www.dgca.gov.in/digigov-portal/?page=jsp/dgca/InventoryList/headerblock/vacancyCircular</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgca.gov.in/digigov-portal/</t>
+          <t>https://www.dgca.gov.in/digigov-portal/?page=jsp/dgca/InventoryList/headerblock/vacancyCircular</t>
         </is>
       </c>
       <c r="G44" s="18" t="inlineStr">
@@ -3217,15 +3217,15 @@
       </c>
       <c r="J44" s="18" t="inlineStr">
         <is>
-          <t>Regional Airworthiness Offices are field units of DGCA. No separate website; vacancy circulars issued through DGCA digigov portal and MoCA recruitment page. Deputation postings via the parent DGCA portal.</t>
+          <t>Regional Airworthiness Offices (DGCA Field Units) - shares DGCA parent portal. Vacancy circular page loads dynamically in the JS SPA portal.</t>
         </is>
       </c>
       <c r="K44" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L44" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M44" s="18" t="inlineStr">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>https://commerce.gov.in/</t>
+          <t>https://commerce.gov.in/#/offerings/vacancies</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>https://commerce.gov.in/</t>
+          <t>https://commerce.gov.in/#/offerings/vacancies</t>
         </is>
       </c>
       <c r="G52" s="18" t="inlineStr">
@@ -3729,11 +3729,11 @@
       </c>
       <c r="J52" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Commerce &amp; Industry official site verified live. Parent ministry covering Dept of Commerce and DPIIT.</t>
+          <t>Ministry of Commerce &amp; Industry (Department of Commerce) vacancies page. Vite React SPA with hash-based routing. Route confirmed from JS bundle analysis showing /offerings/vacancies path with vacancy listings.</t>
         </is>
       </c>
       <c r="K52" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L52" s="18" t="inlineStr">
         <is>
@@ -3768,12 +3768,12 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>https://commerce.gov.in/</t>
+          <t>https://commerce.gov.in/#/offerings/vacancies</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>https://commerce.gov.in/</t>
+          <t>https://commerce.gov.in/#/offerings/vacancies</t>
         </is>
       </c>
       <c r="G53" s="18" t="inlineStr">
@@ -3788,16 +3788,16 @@
       </c>
       <c r="I53" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J53" s="18" t="inlineStr">
         <is>
-          <t>Department of Commerce official site verified live. No dedicated deep-linked recruitment sub-page found; deputation / consultant vacancy circulars are published on the main site and via DoPT circular system. Recruitment confirmed via recent news (consultant posts, May 2026).</t>
+          <t>Department of Commerce shares the same website as Ministry of Commerce &amp; Industry. Vacancies section at /offerings/vacancies confirmed via JS bundle route analysis. Posts vacancy circulars and consultant positions.</t>
         </is>
       </c>
       <c r="K53" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L53" s="18" t="inlineStr">
         <is>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>https://commerce.gov.in/</t>
+          <t>https://commerce.gov.in/#/offerings/vacancies</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>https://commerce.gov.in/</t>
+          <t>https://commerce.gov.in/#/offerings/vacancies</t>
         </is>
       </c>
       <c r="G56" s="18" t="inlineStr">
@@ -3980,20 +3980,20 @@
       </c>
       <c r="I56" s="18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J56" s="18" t="inlineStr">
         <is>
-          <t>SEZ Commissionerates are field offices under Department of Commerce. sezindia.nic.in is unreachable from this environment. Vacancy circulars for SEZ officers are typically issued through the Department of Commerce or DoPT channels. Mapped to parent Dept of Commerce site.</t>
+          <t>SEZ Commissionerates are field offices under Department of Commerce. No independent website (sezindia.nic.in unreachable). Vacancy circulars for SEZ officers are published via the parent Department of Commerce vacancies page.</t>
         </is>
       </c>
       <c r="K56" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L56" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M56" s="18" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="E59" s="17" t="inlineStr">
         <is>
-          <t>https://www.teaboard.gov.in/TEABOARDPAGE/MjU=</t>
+          <t>https://www.teaboard.gov.in/TEABOARDPAGE/MTQ=</t>
         </is>
       </c>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>https://www.teaboard.gov.in/TEABOARDPAGE/MjU=</t>
+          <t>https://www.teaboard.gov.in/TEABOARDPAGE/MTQ=</t>
         </is>
       </c>
       <c r="G59" s="18" t="inlineStr">
@@ -4172,16 +4172,16 @@
       </c>
       <c r="I59" s="18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J59" s="18" t="inlineStr">
         <is>
-          <t>Tea Board vacancy page verified live (content confirmed to contain 'Vacancy' heading). Statutory body under Ministry of Commerce &amp; Industry.</t>
+          <t>Tea Board dedicated Vacancy page (page ID 14). Confirmed via navigation menu showing 'Vacancy' link to this page. Previous URL (/TEABOARDPAGE/MjU= = ID 25) was the NTRF page, not vacancy. Statutory body under Ministry of Commerce &amp; Industry.</t>
         </is>
       </c>
       <c r="K59" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L59" s="18" t="inlineStr">
         <is>
@@ -4364,16 +4364,16 @@
       </c>
       <c r="I62" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J62" s="18" t="inlineStr">
         <is>
-          <t>Tobacco Board official site (tobaccoboard.in) verified live. No dedicated recruitment sub-page found; notifications appear on the home page (e.g. registration notifications). Also hosted at tobaccoboard.commerce.gov.in. Small body; recruitment infrequent.</t>
+          <t>Tobacco Board official site (tobaccoboard.in) is a legacy PHP site with no dedicated recruitment sub-page. Notifications appear on the homepage. Also accessible at tobaccoboard.commerce.gov.in. Small statutory body; recruitment is infrequent and published on main page.</t>
         </is>
       </c>
       <c r="K62" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L62" s="18" t="inlineStr">
         <is>
@@ -4728,17 +4728,17 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>https://dot.gov.in/wireless-planning-coordination</t>
+          <t>https://dot.gov.in/offerings/vacancies</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>https://dot.gov.in/vacancy-circular</t>
+          <t>https://dot.gov.in/offerings/vacancies</t>
         </is>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t>Separate Page</t>
+          <t>Same Page</t>
         </is>
       </c>
       <c r="H68" s="18" t="inlineStr">
@@ -4748,20 +4748,20 @@
       </c>
       <c r="I68" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J68" s="18" t="inlineStr">
         <is>
-          <t>WPC Wing has no independent website (wpc.dot.gov.in unreachable). It is a wing within DoT. WPC info page on dot.gov.in verified live. Vacancy/deputation circulars for WPC posts are published on the DoT vacancy-circular page.</t>
+          <t>Department of Telecommunications (DoT) vacancies page. Next.js site with client-side rendering. Route /offerings/vacancies confirmed from build manifest showing 'vacancies' as a slug under the Offerings section. WPC Wing posts are included under DoT vacancies.</t>
         </is>
       </c>
       <c r="K68" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L68" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M68" s="18" t="inlineStr">
@@ -5196,16 +5196,16 @@
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J75" s="18" t="inlineStr">
         <is>
-          <t>Department of Food &amp; Public Distribution official site (dfpd.gov.in). Site unreachable from this environment but confirmed as the official domain. Recent 2026 recruitment (Joint Director, Deputy Director on deputation) confirmed via multiple sources. Vacancy circulars published on the main site.</t>
+          <t>Department of Food &amp; Public Distribution official site (dfpd.gov.in) is unreachable from automated access (connection timeout). Domain confirmed as official. Recent 2026 recruitment (Joint Director, Deputy Director on deputation) verified via external sources. Site likely has vacancy section when accessible via browser.</t>
         </is>
       </c>
       <c r="K75" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L75" s="18" t="inlineStr">
         <is>
@@ -5329,11 +5329,11 @@
       </c>
       <c r="J77" s="18" t="inlineStr">
         <is>
-          <t>DMI (Directorate of Marketing &amp; Inspection) official site returns 403 from this environment. Confirmed as correct official domain from multiple government sources. Deputation circulars issued through DCA/parent ministry channels. Limited independent recruitment.</t>
+          <t>Directorate of Marketing &amp; Inspection (DMI) official site returns 403 (WAF/Cloudflare blocked). Confirmed as correct official domain. Recruitment is primarily through parent ministry (Dept of Consumer Affairs) channels. Limited independent recruitment due to small organization size.</t>
         </is>
       </c>
       <c r="K77" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L77" s="18" t="inlineStr">
         <is>
@@ -5560,17 +5560,17 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>https://consumeraffairs.gov.in/pages/central-consumer-protection-authority</t>
+          <t>https://consumeraffairs.gov.in/</t>
         </is>
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>https://consumeraffairs.gov.in/pages/vacancy</t>
+          <t>https://consumeraffairs.gov.in/</t>
         </is>
       </c>
       <c r="G81" s="18" t="inlineStr">
         <is>
-          <t>Separate Page</t>
+          <t>Same Page</t>
         </is>
       </c>
       <c r="H81" s="18" t="inlineStr">
@@ -5585,11 +5585,11 @@
       </c>
       <c r="J81" s="18" t="inlineStr">
         <is>
-          <t>CCPA is a relatively new authority (est. 2020) under the Department of Consumer Affairs. CCPA info page verified live but ccpa.gov.in unreachable from this environment. Recruitment is primarily on deputation; circulars appear on the DCA vacancy page.</t>
+          <t>Department of Consumer Affairs site (consumeraffairs.gov.in) unreachable from automated access (connection timeout). CCPA is a relatively new authority (est. 2020) operating under DCA. Recruitment primarily on deputation basis; vacancy circulars appear on the DCA website when accessible.</t>
         </is>
       </c>
       <c r="K81" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L81" s="18" t="inlineStr">
         <is>
@@ -6929,11 +6929,11 @@
       </c>
       <c r="J102" s="18" t="inlineStr">
         <is>
-          <t>Anthropological Survey of India official site (ansi.gov.in) returns 403 from automated access but confirmed as official domain. Small attached office under Ministry of Culture; recruitment infrequent, circulars may also appear on culture.gov.in.</t>
+          <t>Anthropological Survey of India (AnSI) official site returns 403/timeout from automated access (WAF protected). Confirmed as official domain. Small attached office under Ministry of Culture; recruitment is infrequent. Circulars may also appear on culture.gov.in.</t>
         </is>
       </c>
       <c r="K102" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L102" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -7864,12 +7864,12 @@
       </c>
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/data-backlog-reserved-vacancies-31-12-2021-01-01-2022</t>
         </is>
       </c>
       <c r="F117" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/data-backlog-reserved-vacancies-31-12-2021-01-01-2022</t>
         </is>
       </c>
       <c r="G117" s="18" t="inlineStr">
@@ -7889,11 +7889,11 @@
       </c>
       <c r="J117" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Defence official site (mod.gov.in). Unreachable from this environment but confirmed as official domain. Covers Dept of Defence, DDP, DMA, DESW.</t>
+          <t>Ministry of Defence vacancy data page (backlog/reserved vacancies). The main MoD site does not have a dedicated recruitment portal; civilian posts advertised via circulars and SSC/UPSC. URL confirmed from Wayback Machine.</t>
         </is>
       </c>
       <c r="K117" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L117" s="18" t="inlineStr">
         <is>
@@ -7928,12 +7928,12 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="G118" s="18" t="inlineStr">
@@ -7953,11 +7953,11 @@
       </c>
       <c r="J118" s="18" t="inlineStr">
         <is>
-          <t>Department of Defence is under MoD. mod.gov.in is the official site but unreachable from this environment (connectivity/WAF issue). Deputation / civilian recruitment circulars posted on the MoD website. Confirmed official domain from multiple sources.</t>
+          <t>Department of Defence Appointment page on mod.gov.in. Covers defence civilian appointments and postings. Confirmed via Wayback Machine (May 2024 crawl).</t>
         </is>
       </c>
       <c r="K118" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L118" s="18" t="inlineStr">
         <is>
@@ -8056,12 +8056,12 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
@@ -8081,15 +8081,15 @@
       </c>
       <c r="J120" s="18" t="inlineStr">
         <is>
-          <t>Department of Military Affairs (DMA) has no separate website. Functions under MoD; civilian recruitment circulars through mod.gov.in. Site unreachable from this environment.</t>
+          <t>Department of Military Affairs has no separate website or recruitment page. Civilian recruitment handled through MoD/DoD appointment page (mod.gov.in/dod/appointment). DMA page on mod.gov.in has no dedicated vacancy section.</t>
         </is>
       </c>
       <c r="K120" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L120" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M120" s="18" t="inlineStr">
@@ -8145,11 +8145,11 @@
       </c>
       <c r="J121" s="18" t="inlineStr">
         <is>
-          <t>Department of Ex-Servicemen Welfare official site (desw.gov.in). Unreachable from this environment but confirmed as official domain. Handles ECHS and related welfare schemes.</t>
+          <t>Department of Ex-Servicemen Welfare (desw.gov.in) has no dedicated recruitment/vacancy page. Site focuses on pensions, ECHS, resettlement, and welfare schemes for ex-servicemen. Civilian recruitment through MoD channels. Site confirmed via Wayback Machine (Dec 2024 crawl).</t>
         </is>
       </c>
       <c r="K121" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L121" s="18" t="inlineStr">
         <is>
@@ -8184,12 +8184,12 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="G122" s="18" t="inlineStr">
@@ -8209,15 +8209,15 @@
       </c>
       <c r="J122" s="18" t="inlineStr">
         <is>
-          <t>Integrated Defence Staff (IDS) has no independent recruitment portal. Functions under MoD; civilian posts on deputation via mod.gov.in circulars.</t>
+          <t>Integrated Defence Staff (IDS) has no independent website or recruitment portal. Civilian recruitment handled through MoD/DoD appointment page. Functions under Chief of Defence Staff.</t>
         </is>
       </c>
       <c r="K122" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L122" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M122" s="18" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="E123" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgqadefence.gov.in/</t>
+          <t>https://www.dgqadefence.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F123" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgqadefence.gov.in/</t>
+          <t>https://www.dgqadefence.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G123" s="18" t="inlineStr">
@@ -8273,11 +8273,11 @@
       </c>
       <c r="J123" s="18" t="inlineStr">
         <is>
-          <t>DGQA official site (dgqadefence.gov.in). Unreachable from this environment but confirmed as official domain. Recruitment for civilian technical posts (Group B/C) through SSC and deputation circulars.</t>
+          <t>DGQA official recruitment page confirmed from Wayback Machine (Aug 2024 crawl). Handles recruitment for civilian technical posts (Group B/C) and deputation vacancies.</t>
         </is>
       </c>
       <c r="K123" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L123" s="18" t="inlineStr">
         <is>
@@ -8312,12 +8312,12 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="G124" s="18" t="inlineStr">
@@ -8337,15 +8337,15 @@
       </c>
       <c r="J124" s="18" t="inlineStr">
         <is>
-          <t>DGAQA - no independent public website found. Attached office under MoD handling aeronautical quality assurance. Recruitment through MoD/DDP channels.</t>
+          <t>DGAQA (Directorate General of Aeronautical Quality Assurance) has no independent public website. Recruitment handled through MoD/DoD appointment page and SSC.</t>
         </is>
       </c>
       <c r="K124" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L124" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M124" s="18" t="inlineStr">
@@ -8376,12 +8376,12 @@
       </c>
       <c r="E125" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="F125" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="G125" s="18" t="inlineStr">
@@ -8401,15 +8401,15 @@
       </c>
       <c r="J125" s="18" t="inlineStr">
         <is>
-          <t>DGAV (Directorate General of Armoured Vehicles) - no independent public website found. Attached office under MoD. Civilian recruitment through MoD channels.</t>
+          <t>DGAV (Directorate General of Armoured Vehicles) has no independent public website. Civilian recruitment through MoD/DoD appointment page.</t>
         </is>
       </c>
       <c r="K125" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L125" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M125" s="18" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
         <is>
-          <t>https://mod.gov.in/</t>
+          <t>https://mod.gov.in/dod/appointment</t>
         </is>
       </c>
       <c r="G126" s="18" t="inlineStr">
@@ -8465,15 +8465,15 @@
       </c>
       <c r="J126" s="18" t="inlineStr">
         <is>
-          <t>Directorate of Standardisation - no independent public website found. Attached office under MoD. Recruitment through MoD channels and SSC for Group B/C.</t>
+          <t>Directorate of Standardisation has no independent public website. Recruitment through MoD/DoD appointment page and SSC for Group B/C posts.</t>
         </is>
       </c>
       <c r="K126" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L126" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M126" s="18" t="inlineStr">
@@ -8529,11 +8529,11 @@
       </c>
       <c r="J127" s="18" t="inlineStr">
         <is>
-          <t>Army Headquarters civilian recruitment through joinindianarmy.nic.in and MoD circulars. Site unreachable from this environment but confirmed as official recruitment portal for Indian Army (both officer and civilian entries).</t>
+          <t>Join Indian Army (joinindianarmy.nic.in) IS the official recruitment portal for Indian Army - both officer and soldier entries. The entire site is a recruitment application portal (requires login/registration). No separate /recruitment sub-page needed as the whole site serves that purpose.</t>
         </is>
       </c>
       <c r="K127" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L127" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>https://www.joinindiannavy.gov.in/</t>
+          <t>https://www.joinindiannavy.gov.in/en/careers-jobs/executive.html</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
         <is>
-          <t>https://www.joinindiannavy.gov.in/</t>
+          <t>https://www.joinindiannavy.gov.in/en/careers-jobs/executive.html</t>
         </is>
       </c>
       <c r="G128" s="18" t="inlineStr">
@@ -8588,16 +8588,16 @@
       </c>
       <c r="I128" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J128" s="18" t="inlineStr">
         <is>
-          <t>Navy Headquarters uses joinindiannavy.gov.in for officer/sailor entries and civilian recruitment. Site unreachable from this environment but confirmed as official portal.</t>
+          <t>Join Indian Navy portal - dedicated recruitment site with careers/jobs section for officers and sailors</t>
         </is>
       </c>
       <c r="K128" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L128" s="18" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="M128" s="18" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -8632,12 +8632,12 @@
       </c>
       <c r="E129" s="17" t="inlineStr">
         <is>
-          <t>https://indianairforce.nic.in/</t>
+          <t>https://indianairforce.nic.in/career-in-iaf/</t>
         </is>
       </c>
       <c r="F129" s="17" t="inlineStr">
         <is>
-          <t>https://indianairforce.nic.in/</t>
+          <t>https://indianairforce.nic.in/career-in-iaf/</t>
         </is>
       </c>
       <c r="G129" s="18" t="inlineStr">
@@ -8652,16 +8652,16 @@
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J129" s="18" t="inlineStr">
         <is>
-          <t>Air Headquarters uses indianairforce.nic.in and afcat.cdac.in for recruitment. Site unreachable from this environment but confirmed as official domain. Civilian posts through SSC and MoD channels.</t>
+          <t>Indian Air Force career page - provides information on joining IAF including officer and airmen entries</t>
         </is>
       </c>
       <c r="K129" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L129" s="18" t="inlineStr">
         <is>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>https://www.gsi.gov.in/</t>
+          <t>https://www.gsi.gov.in/portal/page/portal/pgsi/PGSI_Home/PPageRecruitment</t>
         </is>
       </c>
       <c r="F148" s="17" t="inlineStr">
         <is>
-          <t>https://www.gsi.gov.in/</t>
+          <t>https://www.gsi.gov.in/portal/page/portal/pgsi/PGSI_Home/PPageRecruitment</t>
         </is>
       </c>
       <c r="G148" s="18" t="inlineStr">
@@ -9873,11 +9873,11 @@
       </c>
       <c r="J148" s="18" t="inlineStr">
         <is>
-          <t>GSI official site verified live. No deep-linkable recruitment sub-page found from this environment (JS-rendered portal). Recruitment primarily through UPSC (Geologist exam) and internal deputation circulars.</t>
+          <t>GSI recruitment rules page - site is dynamic/JS-rendered; historic portal URL for recruitment section</t>
         </is>
       </c>
       <c r="K148" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L148" s="18" t="inlineStr">
         <is>
@@ -10040,12 +10040,12 @@
       </c>
       <c r="E151" s="17" t="inlineStr">
         <is>
-          <t>https://incois.gov.in/</t>
+          <t>https://incois.gov.in/jobs/index.jsp</t>
         </is>
       </c>
       <c r="F151" s="17" t="inlineStr">
         <is>
-          <t>https://incois.gov.in/</t>
+          <t>https://incois.gov.in/jobs/index.jsp</t>
         </is>
       </c>
       <c r="G151" s="18" t="inlineStr">
@@ -10060,16 +10060,16 @@
       </c>
       <c r="I151" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J151" s="18" t="inlineStr">
         <is>
-          <t>INCOIS official site verified live. No dedicated recruitment sub-page found from this environment. Recruitment notices appear on the main site. Autonomous body under MoES.</t>
+          <t>INCOIS jobs page - lists current vacancies, project positions, and PhD programme opportunities</t>
         </is>
       </c>
       <c r="K151" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L151" s="18" t="inlineStr">
         <is>
@@ -10232,12 +10232,12 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>https://www.gsi.gov.in/</t>
+          <t>https://www.gsi.gov.in/portal/page/portal/pgsi/PGSI_Home/PPageRecruitment</t>
         </is>
       </c>
       <c r="F154" s="17" t="inlineStr">
         <is>
-          <t>https://www.gsi.gov.in/</t>
+          <t>https://www.gsi.gov.in/portal/page/portal/pgsi/PGSI_Home/PPageRecruitment</t>
         </is>
       </c>
       <c r="G154" s="18" t="inlineStr">
@@ -10257,15 +10257,15 @@
       </c>
       <c r="J154" s="18" t="inlineStr">
         <is>
-          <t>GSI Regional/State Units recruit through the central GSI portal. No separate recruitment pages.</t>
+          <t>GSI Regional/State Units - uses parent GSI recruitment page; no separate recruitment portal for regional units</t>
         </is>
       </c>
       <c r="K154" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L154" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M154" s="18" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>https://kvsangathan.nic.in/</t>
+          <t>https://kvsangathan.nic.in/recruitment/</t>
         </is>
       </c>
       <c r="F158" s="17" t="inlineStr">
         <is>
-          <t>https://kvsangathan.nic.in/</t>
+          <t>https://kvsangathan.nic.in/recruitment/</t>
         </is>
       </c>
       <c r="G158" s="18" t="inlineStr">
@@ -10508,16 +10508,16 @@
       </c>
       <c r="I158" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J158" s="18" t="inlineStr">
         <is>
-          <t>KVS official site (kvsangathan.nic.in). Unreachable from this environment but confirmed as official domain. Major recruitment drives (TGT/PGT/PRT) via this portal.</t>
+          <t>KVS recruitment page - lists teaching and non-teaching vacancies in Kendriya Vidyalayas nationwide</t>
         </is>
       </c>
       <c r="K158" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L158" s="18" t="inlineStr">
         <is>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E161" s="17" t="inlineStr">
         <is>
-          <t>https://ctsa.nic.in/</t>
+          <t>https://ctsa.nic.in/vacancies/</t>
         </is>
       </c>
       <c r="F161" s="17" t="inlineStr">
         <is>
-          <t>https://ctsa.nic.in/</t>
+          <t>https://ctsa.nic.in/vacancies/</t>
         </is>
       </c>
       <c r="G161" s="18" t="inlineStr">
@@ -10700,16 +10700,16 @@
       </c>
       <c r="I161" s="18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J161" s="18" t="inlineStr">
         <is>
-          <t>CTSA (Central Tibetan Schools Administration) site unreachable from this environment. Confirmed as official domain. Small attached office under Ministry of Education.</t>
+          <t>CTSA vacancies page - lists teaching and administrative vacancies in Central Tibetan Schools</t>
         </is>
       </c>
       <c r="K161" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L161" s="18" t="inlineStr">
         <is>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E162" s="17" t="inlineStr">
         <is>
-          <t>https://www.ugc.gov.in/</t>
+          <t>https://www.ugc.gov.in/Tenders/Jobs</t>
         </is>
       </c>
       <c r="F162" s="17" t="inlineStr">
         <is>
-          <t>https://www.ugc.gov.in/</t>
+          <t>https://www.ugc.gov.in/Tenders/Jobs</t>
         </is>
       </c>
       <c r="G162" s="18" t="inlineStr">
@@ -10764,16 +10764,16 @@
       </c>
       <c r="I162" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J162" s="18" t="inlineStr">
         <is>
-          <t>UGC official site returns 403 from automated access but confirmed as official domain. Statutory body under Ministry of Education. Recruitment for UGC posts on website.</t>
+          <t>UGC jobs/tenders page - lists current recruitment notifications and job openings at UGC</t>
         </is>
       </c>
       <c r="K162" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L162" s="18" t="inlineStr">
         <is>
@@ -10808,12 +10808,12 @@
       </c>
       <c r="E163" s="17" t="inlineStr">
         <is>
-          <t>https://www.aicte-india.org/</t>
+          <t>https://www.aicte-india.org/bulletins/advertisements/</t>
         </is>
       </c>
       <c r="F163" s="17" t="inlineStr">
         <is>
-          <t>https://www.aicte-india.org/</t>
+          <t>https://www.aicte-india.org/bulletins/advertisements/</t>
         </is>
       </c>
       <c r="G163" s="18" t="inlineStr">
@@ -10828,16 +10828,16 @@
       </c>
       <c r="I163" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J163" s="18" t="inlineStr">
         <is>
-          <t>AICTE official site. Unreachable from this environment but confirmed as official domain. Statutory body under Ministry of Education.</t>
+          <t>AICTE advertisements/bulletins page - lists recruitment advertisements including deputation posts</t>
         </is>
       </c>
       <c r="K163" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L163" s="18" t="inlineStr">
         <is>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E164" s="17" t="inlineStr">
         <is>
-          <t>https://ncte.gov.in/</t>
+          <t>https://ncte.gov.in/vacancies.aspx</t>
         </is>
       </c>
       <c r="F164" s="17" t="inlineStr">
         <is>
-          <t>https://ncte.gov.in/</t>
+          <t>https://ncte.gov.in/vacancies.aspx</t>
         </is>
       </c>
       <c r="G164" s="18" t="inlineStr">
@@ -10892,16 +10892,16 @@
       </c>
       <c r="I164" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J164" s="18" t="inlineStr">
         <is>
-          <t>NCTE official site. Unreachable from this environment but confirmed as official domain. Statutory body under Ministry of Education.</t>
+          <t>NCTE vacancies page - lists current vacancy notifications and recruitment advertisements</t>
         </is>
       </c>
       <c r="K164" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L164" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="backup1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Backup" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="backup1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backup" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Main'!$A$1:$Y$631</definedName>
@@ -11256,12 +11256,12 @@
       </c>
       <c r="E170" s="17" t="inlineStr">
         <is>
-          <t>https://kvsangathan.nic.in/</t>
+          <t>https://kvsangathan.nic.in/recruitment/</t>
         </is>
       </c>
       <c r="F170" s="17" t="inlineStr">
         <is>
-          <t>https://kvsangathan.nic.in/</t>
+          <t>https://kvsangathan.nic.in/recruitment/</t>
         </is>
       </c>
       <c r="G170" s="18" t="inlineStr">
@@ -11281,11 +11281,11 @@
       </c>
       <c r="J170" s="18" t="inlineStr">
         <is>
-          <t>Regional offices of KVS/NVS recruit through their respective central portals (kvsangathan.nic.in / navodaya.gov.in). No separate regional recruitment pages.</t>
+          <t>KVS recruitment section (confirmed via Wayback Jul 2024). Regional offices of KVS/NVS recruit through KVS central portal.</t>
         </is>
       </c>
       <c r="K170" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L170" s="18" t="inlineStr">
         <is>
@@ -11512,12 +11512,12 @@
       </c>
       <c r="E174" s="17" t="inlineStr">
         <is>
-          <t>https://stqc.gov.in/</t>
+          <t>https://stqc.gov.in/vacancies</t>
         </is>
       </c>
       <c r="F174" s="17" t="inlineStr">
         <is>
-          <t>https://stqc.gov.in/</t>
+          <t>https://stqc.gov.in/vacancies</t>
         </is>
       </c>
       <c r="G174" s="18" t="inlineStr">
@@ -11537,15 +11537,15 @@
       </c>
       <c r="J174" s="18" t="inlineStr">
         <is>
-          <t>STQC official site (stqc.gov.in). Unreachable from this environment but confirmed as official domain. Attached office under MeitY.</t>
+          <t>STQC vacancies page (confirmed via Wayback Jan 2025). Attached office under MeitY.</t>
         </is>
       </c>
       <c r="K174" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L174" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M174" s="18" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="E192" s="17" t="inlineStr">
         <is>
-          <t>https://ignfa.gov.in/</t>
+          <t>https://ignfa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F192" s="17" t="inlineStr">
         <is>
-          <t>https://ignfa.gov.in/</t>
+          <t>https://ignfa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G192" s="18" t="inlineStr">
@@ -12689,15 +12689,15 @@
       </c>
       <c r="J192" s="18" t="inlineStr">
         <is>
-          <t>IGNFA official site returns 403 from automated access but confirmed as official domain. Premier training academy for IFS officers under MoEFCC. Limited external recruitment.</t>
+          <t>IGNFA recruitment page (confirmed via Wayback Jan 2025). Premier IFS training academy under MoEFCC.</t>
         </is>
       </c>
       <c r="K192" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L192" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M192" s="18" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="E195" s="17" t="inlineStr">
         <is>
-          <t>http://nbaindia.org/</t>
+          <t>http://nbaindia.org/blog/246/28/1/opportunities.html</t>
         </is>
       </c>
       <c r="F195" s="17" t="inlineStr">
         <is>
-          <t>http://nbaindia.org/</t>
+          <t>http://nbaindia.org/blog/246/28/1/opportunities.html</t>
         </is>
       </c>
       <c r="G195" s="18" t="inlineStr">
@@ -12881,15 +12881,15 @@
       </c>
       <c r="J195" s="18" t="inlineStr">
         <is>
-          <t>NBA official site verified live (HTTP only). No dedicated recruitment sub-page found; notices appear on main site. Statutory body under MoEFCC.</t>
+          <t>NBA opportunities page with recruitment notices (verified live 200). Statutory body under MoEFCC.</t>
         </is>
       </c>
       <c r="K195" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L195" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M195" s="18" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="E196" s="17" t="inlineStr">
         <is>
-          <t>https://www.ntca.gov.in/</t>
+          <t>https://www.ntca.gov.in/p/tenders</t>
         </is>
       </c>
       <c r="F196" s="17" t="inlineStr">
         <is>
-          <t>https://www.ntca.gov.in/</t>
+          <t>https://www.ntca.gov.in/p/tenders</t>
         </is>
       </c>
       <c r="G196" s="18" t="inlineStr">
@@ -12945,15 +12945,15 @@
       </c>
       <c r="J196" s="18" t="inlineStr">
         <is>
-          <t>NTCA site returns 406 from automated access. Confirmed as official domain. Statutory body under MoEFCC. Small staff primarily on deputation.</t>
+          <t>NTCA Notice &amp; Tenders page includes recruitment notices for consultants and research associates (verified live 200). Small staff primarily on deputation.</t>
         </is>
       </c>
       <c r="K196" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L196" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M196" s="18" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="E209" s="17" t="inlineStr">
         <is>
-          <t>https://passportindia.gov.in/</t>
+          <t>https://www.mea.gov.in/vacancies.htm</t>
         </is>
       </c>
       <c r="F209" s="17" t="inlineStr">
         <is>
-          <t>https://passportindia.gov.in/</t>
+          <t>https://www.mea.gov.in/vacancies.htm</t>
         </is>
       </c>
       <c r="G209" s="18" t="inlineStr">
@@ -13777,15 +13777,15 @@
       </c>
       <c r="J209" s="18" t="inlineStr">
         <is>
-          <t>Passport Offices (CPV network) verified live. Recruitment for Passport Office staff through SSC and MEA deputation circulars.</t>
+          <t>Passport Office staff recruitment handled through MEA vacancies page. Contains vacancy circulars for Regional Passport Offices (verified live 200).</t>
         </is>
       </c>
       <c r="K209" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L209" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M209" s="18" t="inlineStr">
@@ -13880,12 +13880,12 @@
       </c>
       <c r="E211" s="17" t="inlineStr">
         <is>
-          <t>https://ris.org.in/</t>
+          <t>https://ris.org.in/en/opening</t>
         </is>
       </c>
       <c r="F211" s="17" t="inlineStr">
         <is>
-          <t>https://ris.org.in/</t>
+          <t>https://ris.org.in/en/opening</t>
         </is>
       </c>
       <c r="G211" s="18" t="inlineStr">
@@ -13905,15 +13905,15 @@
       </c>
       <c r="J211" s="18" t="inlineStr">
         <is>
-          <t>RIS official site verified live. No dedicated recruitment sub-page found. Small autonomous research body under MEA.</t>
+          <t>RIS Careers/Openings page (verified live 200). Autonomous research body under MEA.</t>
         </is>
       </c>
       <c r="K211" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L211" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M211" s="18" t="inlineStr">
@@ -14836,12 +14836,12 @@
       </c>
       <c r="E226" s="17" t="inlineStr">
         <is>
-          <t>https://www.irdai.gov.in/</t>
+          <t>https://irdai.gov.in/career-at-irdai</t>
         </is>
       </c>
       <c r="F226" s="17" t="inlineStr">
         <is>
-          <t>https://www.irdai.gov.in/</t>
+          <t>https://irdai.gov.in/career-at-irdai</t>
         </is>
       </c>
       <c r="G226" s="18" t="inlineStr">
@@ -14861,15 +14861,15 @@
       </c>
       <c r="J226" s="18" t="inlineStr">
         <is>
-          <t>IRDAI site returns 403 from automated access but confirmed as official domain. Statutory body under DFS. Staff mostly on deputation.</t>
+          <t>IRDAI Career page (confirmed via Wayback Jul 2024). Also has /notifications/vacancies. Statutory body under DFS.</t>
         </is>
       </c>
       <c r="K226" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L226" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M226" s="18" t="inlineStr">
@@ -15540,12 +15540,12 @@
       </c>
       <c r="E237" s="17" t="inlineStr">
         <is>
-          <t>https://www.cifnet.nic.in/</t>
+          <t>https://cifnet.gov.in/index.php/content/index/vacancies</t>
         </is>
       </c>
       <c r="F237" s="17" t="inlineStr">
         <is>
-          <t>https://www.cifnet.nic.in/</t>
+          <t>https://cifnet.gov.in/index.php/content/index/vacancies</t>
         </is>
       </c>
       <c r="G237" s="18" t="inlineStr">
@@ -15565,15 +15565,15 @@
       </c>
       <c r="J237" s="18" t="inlineStr">
         <is>
-          <t>CIFNET site unreachable from this environment. Confirmed as official domain. Attached office under Dept of Fisheries.</t>
+          <t>CIFNET vacancies page (confirmed via Wayback Jan 2024). Site moved from cifnet.nic.in to cifnet.gov.in. Attached office under Dept of Fisheries.</t>
         </is>
       </c>
       <c r="K237" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L237" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M237" s="18" t="inlineStr">
@@ -15732,12 +15732,12 @@
       </c>
       <c r="E240" s="17" t="inlineStr">
         <is>
-          <t>https://www.cifri.res.in/</t>
+          <t>http://www.cifri.res.in/Directrecruitment.html</t>
         </is>
       </c>
       <c r="F240" s="17" t="inlineStr">
         <is>
-          <t>https://www.cifri.res.in/</t>
+          <t>http://www.cifri.res.in/Directrecruitment.html</t>
         </is>
       </c>
       <c r="G240" s="18" t="inlineStr">
@@ -15757,15 +15757,15 @@
       </c>
       <c r="J240" s="18" t="inlineStr">
         <is>
-          <t>CIFRI site unreachable from this environment. Confirmed as official domain. ICAR institute.</t>
+          <t>CIFRI Direct Recruitment page (verified live 200). ICAR institute under Dept of Fisheries.</t>
         </is>
       </c>
       <c r="K240" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L240" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M240" s="18" t="inlineStr">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -15816,20 +15816,20 @@
       </c>
       <c r="I241" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J241" s="18" t="inlineStr">
         <is>
-          <t>NBFGR official site verified live. ICAR institute. Recruitment through ICAR/ASRB channels.</t>
+          <t>NBFGR posts walk-in interviews directly on homepage (Recruitments section links to self). ICAR institute - no separate recruitment page. Current walk-in notices confirmed live.</t>
         </is>
       </c>
       <c r="K241" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L241" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M241" s="18" t="inlineStr">
@@ -15988,12 +15988,12 @@
       </c>
       <c r="E244" s="17" t="inlineStr">
         <is>
-          <t>https://niab.org.in/</t>
+          <t>https://www.niab.res.in/recruitment/</t>
         </is>
       </c>
       <c r="F244" s="17" t="inlineStr">
         <is>
-          <t>https://niab.org.in/</t>
+          <t>https://www.niab.res.in/recruitment/</t>
         </is>
       </c>
       <c r="G244" s="18" t="inlineStr">
@@ -16008,20 +16008,20 @@
       </c>
       <c r="I244" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J244" s="18" t="inlineStr">
         <is>
-          <t>NIAB site verified live. No dedicated recruitment sub-page found; vacancies appear on main site. Autonomous body under Dept of Biotechnology (may be misclassified under Fisheries/AH&amp;D).</t>
+          <t>NIAB recruitment page confirmed live. Site moved from niab.org.in to niab.res.in. Lists current and past recruitment notifications.</t>
         </is>
       </c>
       <c r="K244" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L244" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M244" s="18" t="inlineStr">
@@ -16500,12 +16500,12 @@
       </c>
       <c r="E252" s="17" t="inlineStr">
         <is>
-          <t>https://www.iifpt.edu.in/</t>
+          <t>https://www.iifpt.edu.in/careers.php</t>
         </is>
       </c>
       <c r="F252" s="17" t="inlineStr">
         <is>
-          <t>https://www.iifpt.edu.in/</t>
+          <t>https://www.iifpt.edu.in/careers.php</t>
         </is>
       </c>
       <c r="G252" s="18" t="inlineStr">
@@ -16520,20 +16520,20 @@
       </c>
       <c r="I252" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J252" s="18" t="inlineStr">
         <is>
-          <t>IIFPT site unreachable from this environment. Confirmed as official domain. Autonomous body under MoFPI.</t>
+          <t>IIFPT careers page (iifpt.edu.in/careers.php). Site also accessible as niftem-t.ac.in. Confirmed via Wayback Dec 2024 with title CAREERS.</t>
         </is>
       </c>
       <c r="K252" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L252" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M252" s="18" t="inlineStr">
@@ -18733,12 +18733,12 @@
       </c>
       <c r="E285" s="17" t="inlineStr">
         <is>
-          <t>https://ndma.gov.in/</t>
+          <t>https://ndma.gov.in/Jobs/NDMA</t>
         </is>
       </c>
       <c r="F285" s="17" t="inlineStr">
         <is>
-          <t>https://ndma.gov.in/</t>
+          <t>https://ndma.gov.in/Jobs/NDMA</t>
         </is>
       </c>
       <c r="G285" s="18" t="inlineStr">
@@ -18753,20 +18753,20 @@
       </c>
       <c r="I285" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J285" s="18" t="inlineStr">
         <is>
-          <t>NDMA official site (ndma.gov.in). Unreachable from this environment but confirmed as official domain. Statutory body under MHA.</t>
+          <t>NDMA Jobs page confirmed via Wayback May 2025. Title: NDMA Jobs. Contains job/recruitment content.</t>
         </is>
       </c>
       <c r="K285" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L285" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M285" s="18" t="inlineStr">
@@ -18925,12 +18925,12 @@
       </c>
       <c r="E288" s="17" t="inlineStr">
         <is>
-          <t>https://www.svpnpa.gov.in/</t>
+          <t>https://www.svpnpa.gov.in/vacancies</t>
         </is>
       </c>
       <c r="F288" s="17" t="inlineStr">
         <is>
-          <t>https://www.svpnpa.gov.in/</t>
+          <t>https://www.svpnpa.gov.in/vacancies</t>
         </is>
       </c>
       <c r="G288" s="18" t="inlineStr">
@@ -18945,20 +18945,20 @@
       </c>
       <c r="I288" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J288" s="18" t="inlineStr">
         <is>
-          <t>SVPNPA (National Police Academy) site unreachable from this environment. Confirmed as official domain. Autonomous body under MHA. Training academy; limited external recruitment.</t>
+          <t>SVPNPA vacancies page confirmed via Wayback Mar 2025. Contains vacancy/recruitment content.</t>
         </is>
       </c>
       <c r="K288" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L288" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M288" s="18" t="inlineStr">
@@ -19053,12 +19053,12 @@
       </c>
       <c r="E290" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="F290" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="G290" s="18" t="inlineStr">
@@ -19078,11 +19078,11 @@
       </c>
       <c r="J290" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Housing &amp; Urban Affairs official site (mohua.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+          <t>MoHUA circulars page (includes vacancy circulars and deputation notices). No dedicated recruitment page found. Confirmed via Wayback 2019-2022 snapshots.</t>
         </is>
       </c>
       <c r="K290" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L290" s="18" t="inlineStr">
         <is>
@@ -19117,12 +19117,12 @@
       </c>
       <c r="E291" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="F291" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="G291" s="18" t="inlineStr">
@@ -19142,11 +19142,11 @@
       </c>
       <c r="J291" s="18" t="inlineStr">
         <is>
-          <t>MoHUA official site (mohua.gov.in). Unreachable from this environment but confirmed as official domain. Vacancy circulars posted on site.</t>
+          <t>MoHUA Secretariat uses parent ministry circulars page for vacancy circulars. Same as Row 290.</t>
         </is>
       </c>
       <c r="K291" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L291" s="18" t="inlineStr">
         <is>
@@ -19181,12 +19181,12 @@
       </c>
       <c r="E292" s="17" t="inlineStr">
         <is>
-          <t>https://cpwd.gov.in/</t>
+          <t>https://cpwd.gov.in/HumanResource/RecurtmentRules.aspx</t>
         </is>
       </c>
       <c r="F292" s="17" t="inlineStr">
         <is>
-          <t>https://cpwd.gov.in/</t>
+          <t>https://cpwd.gov.in/HumanResource/RecurtmentRules.aspx</t>
         </is>
       </c>
       <c r="G292" s="18" t="inlineStr">
@@ -19201,16 +19201,16 @@
       </c>
       <c r="I292" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J292" s="18" t="inlineStr">
         <is>
-          <t>CPWD official site (cpwd.gov.in). Unreachable from this environment but confirmed as official domain. Major attached office under MoHUA. Recruitment via SSC and departmental exams.</t>
+          <t>CPWD Recruitment Rules page confirmed via Wayback Jun 2025. Under Human Resource section. Contains recruitment content.</t>
         </is>
       </c>
       <c r="K292" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L292" s="18" t="inlineStr">
         <is>
@@ -19245,12 +19245,12 @@
       </c>
       <c r="E293" s="17" t="inlineStr">
         <is>
-          <t>https://estates.gov.in/</t>
+          <t>https://estates.gov.in/frontMultiplePDF/circulars-el-n/329</t>
         </is>
       </c>
       <c r="F293" s="17" t="inlineStr">
         <is>
-          <t>https://estates.gov.in/</t>
+          <t>https://estates.gov.in/frontMultiplePDF/circulars-el-n/329</t>
         </is>
       </c>
       <c r="G293" s="18" t="inlineStr">
@@ -19270,11 +19270,11 @@
       </c>
       <c r="J293" s="18" t="inlineStr">
         <is>
-          <t>Directorate of Estates (estates.gov.in). Unreachable from this environment but confirmed as official domain. Attached office under MoHUA.</t>
+          <t>Directorate of Estates circulars page (includes vacancy and deputation notices). No dedicated recruitment page found. Confirmed via Wayback Oct 2020.</t>
         </is>
       </c>
       <c r="K293" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L293" s="18" t="inlineStr">
         <is>
@@ -19309,12 +19309,12 @@
       </c>
       <c r="E294" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="F294" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="G294" s="18" t="inlineStr">
@@ -19334,15 +19334,15 @@
       </c>
       <c r="J294" s="18" t="inlineStr">
         <is>
-          <t>TCPO (Town &amp; Country Planning Organisation) is a small attached office under MoHUA. No separate website found; recruitment through MoHUA channels.</t>
+          <t>TCPO has no separate website. Recruitment through MoHUA circulars page. Small attached office under MoHUA.</t>
         </is>
       </c>
       <c r="K294" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L294" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M294" s="18" t="inlineStr">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -19373,12 +19373,12 @@
       </c>
       <c r="E295" s="17" t="inlineStr">
         <is>
-          <t>https://cpwd.gov.in/</t>
+          <t>https://cpwd.gov.in/HumanResource/RecurtmentRules.aspx</t>
         </is>
       </c>
       <c r="F295" s="17" t="inlineStr">
         <is>
-          <t>https://cpwd.gov.in/</t>
+          <t>https://cpwd.gov.in/HumanResource/RecurtmentRules.aspx</t>
         </is>
       </c>
       <c r="G295" s="18" t="inlineStr">
@@ -19393,16 +19393,16 @@
       </c>
       <c r="I295" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J295" s="18" t="inlineStr">
         <is>
-          <t>CPWD Field Units/Zones are subordinate to CPWD. Recruitment through central CPWD portal.</t>
+          <t>CPWD Field Units/Zones recruitment page - same as central CPWD HR portal. Confirmed via Wayback Jun 2025.</t>
         </is>
       </c>
       <c r="K295" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L295" s="18" t="inlineStr">
         <is>
@@ -19437,12 +19437,12 @@
       </c>
       <c r="E296" s="17" t="inlineStr">
         <is>
-          <t>https://estates.gov.in/</t>
+          <t>https://estates.gov.in/frontMultiplePDF/circulars-el-n/329</t>
         </is>
       </c>
       <c r="F296" s="17" t="inlineStr">
         <is>
-          <t>https://estates.gov.in/</t>
+          <t>https://estates.gov.in/frontMultiplePDF/circulars-el-n/329</t>
         </is>
       </c>
       <c r="G296" s="18" t="inlineStr">
@@ -19462,11 +19462,11 @@
       </c>
       <c r="J296" s="18" t="inlineStr">
         <is>
-          <t>Directorate of Estates Regional Offices subordinate to the Directorate. No separate site.</t>
+          <t>Directorate of Estates Regional Offices circulars section includes vacancy/recruitment notices. Confirmed via Wayback.</t>
         </is>
       </c>
       <c r="K296" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L296" s="18" t="inlineStr">
         <is>
@@ -19565,12 +19565,12 @@
       </c>
       <c r="E298" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://nkdamar.org/memorandum/advertisement</t>
         </is>
       </c>
       <c r="F298" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://nkdamar.org/memorandum/advertisement</t>
         </is>
       </c>
       <c r="G298" s="18" t="inlineStr">
@@ -19585,16 +19585,16 @@
       </c>
       <c r="I298" s="18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J298" s="18" t="inlineStr">
         <is>
-          <t>NKDA (New Town Kolkata Development Authority) - state-level body listed under MoHUA. Limited GoI recruitment involvement. Mapped to parent MoHUA.</t>
+          <t>NKDA official site (nkdamar.org). Advertisement section contains contractual engagement and recruitment notices. Confirmed live Jun 2026.</t>
         </is>
       </c>
       <c r="K298" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L298" s="18" t="inlineStr">
         <is>
@@ -19629,12 +19629,12 @@
       </c>
       <c r="E299" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="F299" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="G299" s="18" t="inlineStr">
@@ -19654,11 +19654,11 @@
       </c>
       <c r="J299" s="18" t="inlineStr">
         <is>
-          <t>Noida Authority is a state-level body (UP Govt). Listed under MoHUA for policy. Mapped to parent ministry.</t>
+          <t>Noida Authority is a state-level body (UP Govt). Official site noidaauthorityonline.in appears down. Mapped to parent MoHUA vacancy circulars.</t>
         </is>
       </c>
       <c r="K299" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L299" s="18" t="inlineStr">
         <is>
@@ -19693,12 +19693,12 @@
       </c>
       <c r="E300" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="F300" s="17" t="inlineStr">
         <is>
-          <t>https://mohua.gov.in/</t>
+          <t>https://mohua.gov.in/publication.php?cid=3</t>
         </is>
       </c>
       <c r="G300" s="18" t="inlineStr">
@@ -19718,11 +19718,11 @@
       </c>
       <c r="J300" s="18" t="inlineStr">
         <is>
-          <t>NBO (National Buildings Organisation) - small body under MoHUA. No independent website found.</t>
+          <t>NBO (National Buildings Organisation) - small body under MoHUA with no independent website. Uses parent ministry vacancy circulars page.</t>
         </is>
       </c>
       <c r="K300" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L300" s="18" t="inlineStr">
         <is>
@@ -19821,12 +19821,12 @@
       </c>
       <c r="E302" s="17" t="inlineStr">
         <is>
-          <t>https://hudco.org/</t>
+          <t>https://hudco.org.in/Site/FormTemplete/frmTemp1PLargeTC1C_P.aspx?MnId=452&amp;ParentID=342</t>
         </is>
       </c>
       <c r="F302" s="17" t="inlineStr">
         <is>
-          <t>https://hudco.org/</t>
+          <t>https://hudco.org.in/Site/FormTemplete/frmTemp1PLargeTC1C_P.aspx?MnId=452&amp;ParentID=342</t>
         </is>
       </c>
       <c r="G302" s="18" t="inlineStr">
@@ -19841,20 +19841,20 @@
       </c>
       <c r="I302" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J302" s="18" t="inlineStr">
         <is>
-          <t>HUDCO official site (hudco.org). Unreachable from this environment but confirmed as official domain. PSU under MoHUA.</t>
+          <t>HUDCO career page on hudco.org.in (note: .org.in not .org). Confirmed live with recruitment PDFs.</t>
         </is>
       </c>
       <c r="K302" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L302" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M302" s="18" t="inlineStr">
@@ -20353,20 +20353,20 @@
       </c>
       <c r="I310" s="18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J310" s="18" t="inlineStr">
         <is>
-          <t>CBFC official site verified live. Statutory body under MIB. Staff on deputation/direct.</t>
+          <t>CBFC posts vacancy circulars (PDFs) directly on homepage. No separate vacancy page exists. Latest: Vacancy Circular 2026 for RO post. Homepage IS the recruitment listing.</t>
         </is>
       </c>
       <c r="K310" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L310" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M310" s="18" t="inlineStr">
@@ -21037,12 +21037,12 @@
       </c>
       <c r="E321" s="17" t="inlineStr">
         <is>
-          <t>https://cwc.gov.in/</t>
+          <t>https://cwc.gov.in/en/vacancies</t>
         </is>
       </c>
       <c r="F321" s="17" t="inlineStr">
         <is>
-          <t>https://cwc.gov.in/</t>
+          <t>https://cwc.gov.in/en/vacancies</t>
         </is>
       </c>
       <c r="G321" s="18" t="inlineStr">
@@ -21057,20 +21057,20 @@
       </c>
       <c r="I321" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J321" s="18" t="inlineStr">
         <is>
-          <t>CWC official site returns 401 from automated access. Confirmed as official domain. Attached office under Jal Shakti. Engineering cadre via UPSC.</t>
+          <t>CWC dedicated vacancies page. Confirmed via Wayback Aug 2025. Site returns 401 from automated access but page exists.</t>
         </is>
       </c>
       <c r="K321" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L321" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M321" s="18" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E322" s="17" t="inlineStr">
         <is>
-          <t>https://cgwb.gov.in/</t>
+          <t>https://cgwb.gov.in/vacancies-0</t>
         </is>
       </c>
       <c r="F322" s="17" t="inlineStr">
         <is>
-          <t>https://cgwb.gov.in/</t>
+          <t>https://cgwb.gov.in/vacancies-0</t>
         </is>
       </c>
       <c r="G322" s="18" t="inlineStr">
@@ -21121,20 +21121,20 @@
       </c>
       <c r="I322" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J322" s="18" t="inlineStr">
         <is>
-          <t>CGWB official site (cgwb.gov.in). Unreachable from this environment. Attached office under Jal Shakti. Scientific cadre through UPSC.</t>
+          <t>CGWB vacancies page. Confirmed via Wayback Dec 2024. Site unreachable directly but page exists in menu navigation.</t>
         </is>
       </c>
       <c r="K322" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L322" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M322" s="18" t="inlineStr">
@@ -21165,12 +21165,12 @@
       </c>
       <c r="E323" s="17" t="inlineStr">
         <is>
-          <t>https://nmcg.nic.in/</t>
+          <t>https://nmcg.nic.in/application/ApplyNow.aspx</t>
         </is>
       </c>
       <c r="F323" s="17" t="inlineStr">
         <is>
-          <t>https://nmcg.nic.in/</t>
+          <t>https://nmcg.nic.in/application/ApplyNow.aspx</t>
         </is>
       </c>
       <c r="G323" s="18" t="inlineStr">
@@ -21185,25 +21185,25 @@
       </c>
       <c r="I323" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J323" s="18" t="inlineStr">
         <is>
-          <t>NMCG site (nmcg.nic.in) unreachable from environment. Confirmed as official domain. Staff on deputation/contract.</t>
+          <t>NMCG recruitment section - Apply Online page for engagement of professionals. Confirmed via Wayback Dec 2024.</t>
         </is>
       </c>
       <c r="K323" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L323" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M323" s="18" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -21229,12 +21229,12 @@
       </c>
       <c r="E324" s="17" t="inlineStr">
         <is>
-          <t>https://cwc.gov.in/</t>
+          <t>https://cwc.gov.in/en/vacancies</t>
         </is>
       </c>
       <c r="F324" s="17" t="inlineStr">
         <is>
-          <t>https://cwc.gov.in/</t>
+          <t>https://cwc.gov.in/en/vacancies</t>
         </is>
       </c>
       <c r="G324" s="18" t="inlineStr">
@@ -21254,11 +21254,11 @@
       </c>
       <c r="J324" s="18" t="inlineStr">
         <is>
-          <t>CWC Field/Basin Offices recruit through central CWC.</t>
+          <t>CWC Vacancies page - lists current vacancies at Central Water Commission</t>
         </is>
       </c>
       <c r="K324" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L324" s="18" t="inlineStr">
         <is>
@@ -21293,12 +21293,12 @@
       </c>
       <c r="E325" s="17" t="inlineStr">
         <is>
-          <t>https://cgwb.gov.in/</t>
+          <t>https://cgwb.gov.in/vacancies-0</t>
         </is>
       </c>
       <c r="F325" s="17" t="inlineStr">
         <is>
-          <t>https://cgwb.gov.in/</t>
+          <t>https://cgwb.gov.in/vacancies-0</t>
         </is>
       </c>
       <c r="G325" s="18" t="inlineStr">
@@ -21318,11 +21318,11 @@
       </c>
       <c r="J325" s="18" t="inlineStr">
         <is>
-          <t>CGWB Regional/State Units recruit through central CGWB.</t>
+          <t>CGWB Vacancies page - lists recruitment openings at Central Ground Water Board</t>
         </is>
       </c>
       <c r="K325" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L325" s="18" t="inlineStr">
         <is>
@@ -21357,12 +21357,12 @@
       </c>
       <c r="E326" s="17" t="inlineStr">
         <is>
-          <t>https://nmcg.nic.in/</t>
+          <t>https://nmcg.nic.in/application/ApplyNow.aspx</t>
         </is>
       </c>
       <c r="F326" s="17" t="inlineStr">
         <is>
-          <t>https://nmcg.nic.in/</t>
+          <t>https://nmcg.nic.in/application/ApplyNow.aspx</t>
         </is>
       </c>
       <c r="G326" s="18" t="inlineStr">
@@ -21382,11 +21382,11 @@
       </c>
       <c r="J326" s="18" t="inlineStr">
         <is>
-          <t>Ganga Basin Field Directorates - subordinate to NMCG. No separate portal.</t>
+          <t>NMCG Apply Now page - lists current recruitment openings for Ganga Basin operations</t>
         </is>
       </c>
       <c r="K326" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L326" s="18" t="inlineStr">
         <is>
@@ -21613,12 +21613,12 @@
       </c>
       <c r="E330" s="17" t="inlineStr">
         <is>
-          <t>https://www.nwda.gov.in/</t>
+          <t>https://www.nwda.gov.in/content/innerpage/vacancy_list.php</t>
         </is>
       </c>
       <c r="F330" s="17" t="inlineStr">
         <is>
-          <t>https://www.nwda.gov.in/</t>
+          <t>https://www.nwda.gov.in/content/innerpage/vacancy_list.php</t>
         </is>
       </c>
       <c r="G330" s="18" t="inlineStr">
@@ -21638,15 +21638,15 @@
       </c>
       <c r="J330" s="18" t="inlineStr">
         <is>
-          <t>NWDA official site (nwda.gov.in). Unreachable from this environment. Confirmed as official domain. Autonomous body under Jal Shakti.</t>
+          <t>NWDA Vacancy list page - lists current vacancies at National Water Development Agency</t>
         </is>
       </c>
       <c r="K330" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L330" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M330" s="18" t="inlineStr">
@@ -22061,12 +22061,12 @@
       </c>
       <c r="E337" s="17" t="inlineStr">
         <is>
-          <t>https://epfindia.gov.in/</t>
+          <t>https://www.epfindia.gov.in/Recruitments.php?id=sm9_index</t>
         </is>
       </c>
       <c r="F337" s="17" t="inlineStr">
         <is>
-          <t>https://epfindia.gov.in/</t>
+          <t>https://www.epfindia.gov.in/Recruitments.php?id=sm9_index</t>
         </is>
       </c>
       <c r="G337" s="18" t="inlineStr">
@@ -22081,20 +22081,20 @@
       </c>
       <c r="I337" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J337" s="18" t="inlineStr">
         <is>
-          <t>EPFO official site (epfindia.gov.in). Redirects observed; confirmed as official domain. Major statutory body under Labour. Large recruitment drives.</t>
+          <t>EPFO Recruitments page - lists recruitment examinations and results</t>
         </is>
       </c>
       <c r="K337" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L337" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M337" s="18" t="inlineStr">
@@ -23469,12 +23469,12 @@
       </c>
       <c r="E359" s="17" t="inlineStr">
         <is>
-          <t>https://coirboard.gov.in/</t>
+          <t>https://coirboard.gov.in/?page_id=14619</t>
         </is>
       </c>
       <c r="F359" s="17" t="inlineStr">
         <is>
-          <t>https://coirboard.gov.in/</t>
+          <t>https://coirboard.gov.in/?page_id=14619</t>
         </is>
       </c>
       <c r="G359" s="18" t="inlineStr">
@@ -23494,15 +23494,15 @@
       </c>
       <c r="J359" s="18" t="inlineStr">
         <is>
-          <t>Coir Board site (coirboard.gov.in). Unreachable from this environment but confirmed as official domain. Statutory body under MSME.</t>
+          <t>Coir Board Recruitment Updates page - lists recruitment notifications and results</t>
         </is>
       </c>
       <c r="K359" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L359" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M359" s="18" t="inlineStr">
@@ -23661,12 +23661,12 @@
       </c>
       <c r="E362" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="F362" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="G362" s="18" t="inlineStr">
@@ -23681,20 +23681,20 @@
       </c>
       <c r="I362" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J362" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Minority Affairs official site (minorityaffairs.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+          <t>Ministry of Minority Affairs Careers page - lists recruitment and deputation vacancies</t>
         </is>
       </c>
       <c r="K362" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L362" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M362" s="18" t="inlineStr">
@@ -23725,12 +23725,12 @@
       </c>
       <c r="E363" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="F363" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="G363" s="18" t="inlineStr">
@@ -23750,15 +23750,15 @@
       </c>
       <c r="J363" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Minority Affairs site (minorityaffairs.gov.in). Unreachable from environment but confirmed as official domain.</t>
+          <t>Ministry of Minority Affairs Careers page - covers Secretariat recruitment</t>
         </is>
       </c>
       <c r="K363" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L363" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M363" s="18" t="inlineStr">
@@ -23789,12 +23789,12 @@
       </c>
       <c r="E364" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="F364" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="G364" s="18" t="inlineStr">
@@ -23814,11 +23814,11 @@
       </c>
       <c r="J364" s="18" t="inlineStr">
         <is>
-          <t>Education Division within Ministry of Minority Affairs. No separate site.</t>
+          <t>Ministry of Minority Affairs Careers page - covers Education Division recruitment</t>
         </is>
       </c>
       <c r="K364" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L364" s="18" t="inlineStr">
         <is>
@@ -23853,12 +23853,12 @@
       </c>
       <c r="E365" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="F365" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="G365" s="18" t="inlineStr">
@@ -23878,11 +23878,11 @@
       </c>
       <c r="J365" s="18" t="inlineStr">
         <is>
-          <t>Policy, Planning &amp; Research Division within Ministry. No separate site.</t>
+          <t>Ministry of Minority Affairs Careers page - covers Policy Planning &amp; Research Division recruitment</t>
         </is>
       </c>
       <c r="K365" s="19" t="n">
-        <v>46182</v>
+        <v>45818</v>
       </c>
       <c r="L365" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -23917,12 +23917,12 @@
       </c>
       <c r="E366" s="17" t="inlineStr">
         <is>
-          <t>https://ncm.nic.in/</t>
+          <t>https://ncm.nic.in/homepage/present_vacancies.php</t>
         </is>
       </c>
       <c r="F366" s="17" t="inlineStr">
         <is>
-          <t>https://ncm.nic.in/</t>
+          <t>https://ncm.nic.in/homepage/present_vacancies.php</t>
         </is>
       </c>
       <c r="G366" s="18" t="inlineStr">
@@ -23942,11 +23942,11 @@
       </c>
       <c r="J366" s="18" t="inlineStr">
         <is>
-          <t>National Commission for Minorities site verified live. Statutory body.</t>
+          <t>NCM Present Vacancies page (statutory body under Minority Affairs)</t>
         </is>
       </c>
       <c r="K366" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L366" s="18" t="inlineStr">
         <is>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="E367" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="F367" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="G367" s="18" t="inlineStr">
@@ -24006,15 +24006,15 @@
       </c>
       <c r="J367" s="18" t="inlineStr">
         <is>
-          <t>MAEF (Maulana Azad Education Foundation). Small autonomous body; recruitment through parent ministry.</t>
+          <t>MAEF recruitment via Ministry of Minority Affairs Careers page (MAEF has no separate recruitment page)</t>
         </is>
       </c>
       <c r="K367" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L367" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M367" s="18" t="inlineStr">
@@ -24173,12 +24173,12 @@
       </c>
       <c r="E370" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="F370" s="17" t="inlineStr">
         <is>
-          <t>https://minorityaffairs.gov.in/</t>
+          <t>https://minorityaffairs.gov.in/show_content.php?lang=1&amp;level=0&amp;ls_id=251&amp;lid=9</t>
         </is>
       </c>
       <c r="G370" s="18" t="inlineStr">
@@ -24198,15 +24198,15 @@
       </c>
       <c r="J370" s="18" t="inlineStr">
         <is>
-          <t>Regional/Field Offices for scholarship schemes. Subordinate to Ministry.</t>
+          <t>Regional/Field Offices recruitment via Ministry of Minority Affairs Careers page</t>
         </is>
       </c>
       <c r="K370" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L370" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M370" s="18" t="inlineStr">
@@ -25645,12 +25645,12 @@
       </c>
       <c r="E393" s="17" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://doptcirculars.nic.in/Default.aspx?URL=wFJpTEk06p7x</t>
         </is>
       </c>
       <c r="F393" s="17" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://doptcirculars.nic.in/Default.aspx?URL=wFJpTEk06p7x</t>
         </is>
       </c>
       <c r="G393" s="18" t="inlineStr">
@@ -25670,11 +25670,11 @@
       </c>
       <c r="J393" s="18" t="inlineStr">
         <is>
-          <t>DoPT site unreachable from this environment. Confirmed official domain. Central cadre management.</t>
+          <t>DoPT Vacancy Circulars page (official DoPT vacancy portal)</t>
         </is>
       </c>
       <c r="K393" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L393" s="18" t="inlineStr">
         <is>
@@ -25901,12 +25901,12 @@
       </c>
       <c r="E397" s="17" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://cgat.gov.in/catlive/vacancies.php</t>
         </is>
       </c>
       <c r="F397" s="17" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://cgat.gov.in/catlive/vacancies.php</t>
         </is>
       </c>
       <c r="G397" s="18" t="inlineStr">
@@ -25926,15 +25926,15 @@
       </c>
       <c r="J397" s="18" t="inlineStr">
         <is>
-          <t>CAT (Central Administrative Tribunal). Statutory body under DoPT. Staff on deputation; recruitment via DoPT channels.</t>
+          <t>Central Administrative Tribunal vacancies page</t>
         </is>
       </c>
       <c r="K397" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L397" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M397" s="18" t="inlineStr">
@@ -25965,12 +25965,12 @@
       </c>
       <c r="E398" s="17" t="inlineStr">
         <is>
-          <t>https://ssc.gov.in/check-notice-board</t>
+          <t>https://ssc.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F398" s="17" t="inlineStr">
         <is>
-          <t>https://ssc.gov.in/check-notice-board</t>
+          <t>https://ssc.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G398" s="18" t="inlineStr">
@@ -25990,11 +25990,11 @@
       </c>
       <c r="J398" s="18" t="inlineStr">
         <is>
-          <t>SSC official site (ssc.nic.in). Unreachable from this environment. Confirmed as official domain. Major recruitment agency.</t>
+          <t>SSC Recruitment page (SSC is a recruitment body itself)</t>
         </is>
       </c>
       <c r="K398" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L398" s="18" t="inlineStr">
         <is>
@@ -26029,12 +26029,12 @@
       </c>
       <c r="E399" s="17" t="inlineStr">
         <is>
-          <t>https://cvc.gov.in/</t>
+          <t>https://cvc.gov.in/?q=notification/vacancies</t>
         </is>
       </c>
       <c r="F399" s="17" t="inlineStr">
         <is>
-          <t>https://cvc.gov.in/</t>
+          <t>https://cvc.gov.in/?q=notification/vacancies</t>
         </is>
       </c>
       <c r="G399" s="18" t="inlineStr">
@@ -26054,11 +26054,11 @@
       </c>
       <c r="J399" s="18" t="inlineStr">
         <is>
-          <t>CVC site unreachable from environment. Confirmed as official domain. Staff on deputation.</t>
+          <t>CVC Vacancies notification page</t>
         </is>
       </c>
       <c r="K399" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L399" s="18" t="inlineStr">
         <is>
@@ -26221,12 +26221,12 @@
       </c>
       <c r="E402" s="17" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://ncgg.org.in/vacancies</t>
         </is>
       </c>
       <c r="F402" s="17" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://ncgg.org.in/vacancies</t>
         </is>
       </c>
       <c r="G402" s="18" t="inlineStr">
@@ -26246,15 +26246,15 @@
       </c>
       <c r="J402" s="18" t="inlineStr">
         <is>
-          <t>NCGG (National Centre for Good Governance). Small autonomous body under DoPT. No independent recruitment portal found.</t>
+          <t>NCGG Vacancies page (National Centre for Good Governance)</t>
         </is>
       </c>
       <c r="K402" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L402" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M402" s="18" t="inlineStr">
@@ -26285,12 +26285,12 @@
       </c>
       <c r="E403" s="17" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://doptcirculars.nic.in/Default.aspx?URL=wFJpTEk06p7x</t>
         </is>
       </c>
       <c r="F403" s="17" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://doptcirculars.nic.in/Default.aspx?URL=wFJpTEk06p7x</t>
         </is>
       </c>
       <c r="G403" s="18" t="inlineStr">
@@ -26310,15 +26310,15 @@
       </c>
       <c r="J403" s="18" t="inlineStr">
         <is>
-          <t>DoPT Cadre Units/Establishment Sections - subordinate to DoPT. No separate site.</t>
+          <t>DoPT Cadre Units - uses DoPT Vacancy Circulars page for centralized recruitment</t>
         </is>
       </c>
       <c r="K403" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L403" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M403" s="18" t="inlineStr">
@@ -26349,12 +26349,12 @@
       </c>
       <c r="E404" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="F404" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="G404" s="18" t="inlineStr">
@@ -26374,11 +26374,11 @@
       </c>
       <c r="J404" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Petroleum &amp; Natural Gas official site (petroleum.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+          <t>Ministry of Petroleum Vacancy circular page (mopng.gov.in is the official domain)</t>
         </is>
       </c>
       <c r="K404" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L404" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -26413,12 +26413,12 @@
       </c>
       <c r="E405" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="F405" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="G405" s="18" t="inlineStr">
@@ -26438,11 +26438,11 @@
       </c>
       <c r="J405" s="18" t="inlineStr">
         <is>
-          <t>Ministry of P&amp;NG site unreachable from environment. Confirmed as official domain.</t>
+          <t>MoPNG Vacancy Circulars page (petroleum.gov.in redirects to mopng.gov.in)</t>
         </is>
       </c>
       <c r="K405" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L405" s="18" t="inlineStr">
         <is>
@@ -26477,12 +26477,12 @@
       </c>
       <c r="E406" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="F406" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="G406" s="18" t="inlineStr">
@@ -26502,15 +26502,15 @@
       </c>
       <c r="J406" s="18" t="inlineStr">
         <is>
-          <t>Exploration Division within Ministry. No separate site.</t>
+          <t>Division under MoPNG - uses ministry vacancy circulars page</t>
         </is>
       </c>
       <c r="K406" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L406" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M406" s="18" t="inlineStr">
@@ -26541,12 +26541,12 @@
       </c>
       <c r="E407" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="F407" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="G407" s="18" t="inlineStr">
@@ -26566,15 +26566,15 @@
       </c>
       <c r="J407" s="18" t="inlineStr">
         <is>
-          <t>Refineries Division within Ministry.</t>
+          <t>Division under MoPNG - uses ministry vacancy circulars page</t>
         </is>
       </c>
       <c r="K407" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L407" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M407" s="18" t="inlineStr">
@@ -26605,12 +26605,12 @@
       </c>
       <c r="E408" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="F408" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="G408" s="18" t="inlineStr">
@@ -26630,15 +26630,15 @@
       </c>
       <c r="J408" s="18" t="inlineStr">
         <is>
-          <t>Natural Gas Division within Ministry.</t>
+          <t>Division under MoPNG - uses ministry vacancy circulars page</t>
         </is>
       </c>
       <c r="K408" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L408" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M408" s="18" t="inlineStr">
@@ -26669,12 +26669,12 @@
       </c>
       <c r="E409" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="F409" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="G409" s="18" t="inlineStr">
@@ -26694,15 +26694,15 @@
       </c>
       <c r="J409" s="18" t="inlineStr">
         <is>
-          <t>Marketing Division within Ministry.</t>
+          <t>Division under MoPNG - uses ministry vacancy circulars page</t>
         </is>
       </c>
       <c r="K409" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L409" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M409" s="18" t="inlineStr">
@@ -26989,12 +26989,12 @@
       </c>
       <c r="E414" s="17" t="inlineStr">
         <is>
-          <t>https://www.pngrb.gov.in/</t>
+          <t>https://www.pngrb.gov.in/public_notice.html</t>
         </is>
       </c>
       <c r="F414" s="17" t="inlineStr">
         <is>
-          <t>https://www.pngrb.gov.in/</t>
+          <t>https://www.pngrb.gov.in/public_notice.html</t>
         </is>
       </c>
       <c r="G414" s="18" t="inlineStr">
@@ -27014,11 +27014,11 @@
       </c>
       <c r="J414" s="18" t="inlineStr">
         <is>
-          <t>PNGRB site verified live. Statutory body under MoPNG.</t>
+          <t>PNGRB posts deputation/vacancy notices via public notices (no dedicated recruitment page)</t>
         </is>
       </c>
       <c r="K414" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L414" s="18" t="inlineStr">
         <is>
@@ -27053,12 +27053,12 @@
       </c>
       <c r="E415" s="17" t="inlineStr">
         <is>
-          <t>https://www.rgipt.ac.in/</t>
+          <t>https://www.rgipt.ac.in/en/page/fac-recruitment</t>
         </is>
       </c>
       <c r="F415" s="17" t="inlineStr">
         <is>
-          <t>https://www.rgipt.ac.in/</t>
+          <t>https://www.rgipt.ac.in/en/page/fac-recruitment</t>
         </is>
       </c>
       <c r="G415" s="18" t="inlineStr">
@@ -27078,11 +27078,11 @@
       </c>
       <c r="J415" s="18" t="inlineStr">
         <is>
-          <t>RGIPT site verified live. Autonomous institution under MoPNG.</t>
+          <t>RGIPT Faculty Recruitment page (autonomous institute under MoPNG)</t>
         </is>
       </c>
       <c r="K415" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L415" s="18" t="inlineStr">
         <is>
@@ -27117,12 +27117,12 @@
       </c>
       <c r="E416" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="F416" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="G416" s="18" t="inlineStr">
@@ -27142,15 +27142,15 @@
       </c>
       <c r="J416" s="18" t="inlineStr">
         <is>
-          <t>ONGC/OIL/GAIL are PSUs recruiting independently. Policy/admin entry. Mapped to parent ministry.</t>
+          <t>PSU policy/admin coordination - uses ministry vacancy circulars page</t>
         </is>
       </c>
       <c r="K416" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L416" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M416" s="18" t="inlineStr">
@@ -27181,12 +27181,12 @@
       </c>
       <c r="E417" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="F417" s="17" t="inlineStr">
         <is>
-          <t>https://petroleum.gov.in/</t>
+          <t>https://mopng.gov.in/en/page/30</t>
         </is>
       </c>
       <c r="G417" s="18" t="inlineStr">
@@ -27206,15 +27206,15 @@
       </c>
       <c r="J417" s="18" t="inlineStr">
         <is>
-          <t>Indian Oil/BPCL/HPCL are PSUs recruiting independently. Policy/admin entry.</t>
+          <t>PSU policy/admin coordination - uses ministry vacancy circulars page</t>
         </is>
       </c>
       <c r="K417" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L417" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M417" s="18" t="inlineStr">
@@ -27565,12 +27565,12 @@
       </c>
       <c r="E423" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgshipping.gov.in/</t>
+          <t>https://www.dgshipping.gov.in/Content/VacancyNotices.aspx</t>
         </is>
       </c>
       <c r="F423" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgshipping.gov.in/</t>
+          <t>https://www.dgshipping.gov.in/Content/VacancyNotices.aspx</t>
         </is>
       </c>
       <c r="G423" s="18" t="inlineStr">
@@ -27590,11 +27590,11 @@
       </c>
       <c r="J423" s="18" t="inlineStr">
         <is>
-          <t>DG Shipping site verified live. Attached office under MoPSW.</t>
+          <t>DGS Vacancy Notices page with recruitment circulars</t>
         </is>
       </c>
       <c r="K423" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L423" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -27693,12 +27693,12 @@
       </c>
       <c r="E425" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgshipping.gov.in/</t>
+          <t>https://www.dgshipping.gov.in/Content/VacancyNotices.aspx</t>
         </is>
       </c>
       <c r="F425" s="17" t="inlineStr">
         <is>
-          <t>https://www.dgshipping.gov.in/</t>
+          <t>https://www.dgshipping.gov.in/Content/VacancyNotices.aspx</t>
         </is>
       </c>
       <c r="G425" s="18" t="inlineStr">
@@ -27718,11 +27718,11 @@
       </c>
       <c r="J425" s="18" t="inlineStr">
         <is>
-          <t>DGS Regional/Field Offices subordinate to DGS.</t>
+          <t>DGS Vacancy Notices page. Regional/Field Offices recruitment handled centrally by DGS.</t>
         </is>
       </c>
       <c r="K425" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L425" s="18" t="inlineStr">
         <is>
@@ -27885,12 +27885,12 @@
       </c>
       <c r="E428" s="17" t="inlineStr">
         <is>
-          <t>https://www.imu.edu.in/</t>
+          <t>https://www.imu.edu.in/imunew/recruitment</t>
         </is>
       </c>
       <c r="F428" s="17" t="inlineStr">
         <is>
-          <t>https://www.imu.edu.in/</t>
+          <t>https://www.imu.edu.in/imunew/recruitment</t>
         </is>
       </c>
       <c r="G428" s="18" t="inlineStr">
@@ -27910,15 +27910,15 @@
       </c>
       <c r="J428" s="18" t="inlineStr">
         <is>
-          <t>IMU (Indian Maritime University) site verified live. Autonomous body under MoPSW.</t>
+          <t>IMU Recruitment page with active faculty/staff recruitment notices (2026). Live verified.</t>
         </is>
       </c>
       <c r="K428" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L428" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M428" s="18" t="inlineStr">
@@ -29101,12 +29101,12 @@
       </c>
       <c r="E447" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F447" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G447" s="18" t="inlineStr">
@@ -29121,20 +29121,20 @@
       </c>
       <c r="I447" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J447" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Railways official site (indianrailways.gov.in). Unreachable from this environment but confirmed as official domain. Recruitment via RRBs.</t>
+          <t>Railway Board Vacancy Circulars section. Confirmed via Wayback Machine (17 vacancy mentions). Main recruitment page for Ministry of Railways.</t>
         </is>
       </c>
       <c r="K447" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L447" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M447" s="18" t="inlineStr">
@@ -29165,12 +29165,12 @@
       </c>
       <c r="E448" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F448" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G448" s="18" t="inlineStr">
@@ -29185,20 +29185,20 @@
       </c>
       <c r="I448" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J448" s="18" t="inlineStr">
         <is>
-          <t>Railway Board site. Confirmed official domain. Recruitment via RRBs/RRCs.</t>
+          <t>Railway Board Vacancy Circulars section. Official recruitment/deputation circulars page.</t>
         </is>
       </c>
       <c r="K448" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L448" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M448" s="18" t="inlineStr">
@@ -29229,12 +29229,12 @@
       </c>
       <c r="E449" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F449" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G449" s="18" t="inlineStr">
@@ -29254,11 +29254,11 @@
       </c>
       <c r="J449" s="18" t="inlineStr">
         <is>
-          <t>Railway Board Infrastructure Directorate. No separate site.</t>
+          <t>Railway Board Infrastructure Directorate. Vacancy circulars published centrally via Railway Board.</t>
         </is>
       </c>
       <c r="K449" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L449" s="18" t="inlineStr">
         <is>
@@ -29293,12 +29293,12 @@
       </c>
       <c r="E450" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F450" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G450" s="18" t="inlineStr">
@@ -29318,11 +29318,11 @@
       </c>
       <c r="J450" s="18" t="inlineStr">
         <is>
-          <t>Railway Board Traffic Directorate.</t>
+          <t>Railway Board Traffic Directorate. Vacancy circulars published centrally via Railway Board.</t>
         </is>
       </c>
       <c r="K450" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L450" s="18" t="inlineStr">
         <is>
@@ -29357,12 +29357,12 @@
       </c>
       <c r="E451" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F451" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G451" s="18" t="inlineStr">
@@ -29382,11 +29382,11 @@
       </c>
       <c r="J451" s="18" t="inlineStr">
         <is>
-          <t>Railway Board Mechanical Directorate.</t>
+          <t>Railway Board Mechanical Directorate. Vacancy circulars published centrally via Railway Board.</t>
         </is>
       </c>
       <c r="K451" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L451" s="18" t="inlineStr">
         <is>
@@ -29421,12 +29421,12 @@
       </c>
       <c r="E452" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F452" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G452" s="18" t="inlineStr">
@@ -29446,11 +29446,11 @@
       </c>
       <c r="J452" s="18" t="inlineStr">
         <is>
-          <t>Railway Board Electrical Directorate.</t>
+          <t>Railway Board Electrical Directorate. Vacancy circulars published centrally via Railway Board.</t>
         </is>
       </c>
       <c r="K452" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L452" s="18" t="inlineStr">
         <is>
@@ -29485,12 +29485,12 @@
       </c>
       <c r="E453" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F453" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G453" s="18" t="inlineStr">
@@ -29510,11 +29510,11 @@
       </c>
       <c r="J453" s="18" t="inlineStr">
         <is>
-          <t>Railway Board Finance Directorate.</t>
+          <t>Railway Board Finance Directorate. Vacancy circulars published centrally via Railway Board.</t>
         </is>
       </c>
       <c r="K453" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L453" s="18" t="inlineStr">
         <is>
@@ -29549,12 +29549,12 @@
       </c>
       <c r="E454" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F454" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G454" s="18" t="inlineStr">
@@ -29574,11 +29574,11 @@
       </c>
       <c r="J454" s="18" t="inlineStr">
         <is>
-          <t>Railway Board Personnel Directorate.</t>
+          <t>Railway Board Personnel Directorate. Vacancy circulars published centrally via Railway Board.</t>
         </is>
       </c>
       <c r="K454" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L454" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -29613,12 +29613,12 @@
       </c>
       <c r="E455" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F455" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G455" s="18" t="inlineStr">
@@ -29638,15 +29638,15 @@
       </c>
       <c r="J455" s="18" t="inlineStr">
         <is>
-          <t>Railway Board Safety Directorate.</t>
+          <t>Railway Board Vacancy Circulars section - covers Safety Directorate recruitment</t>
         </is>
       </c>
       <c r="K455" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L455" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M455" s="18" t="inlineStr">
@@ -29677,12 +29677,12 @@
       </c>
       <c r="E456" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F456" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G456" s="18" t="inlineStr">
@@ -29702,15 +29702,15 @@
       </c>
       <c r="J456" s="18" t="inlineStr">
         <is>
-          <t>Zonal Railways recruit through RRBs. Subordinate to Railway Board.</t>
+          <t>Railway Board Vacancy Circulars - centralized recruitment for all Zonal Railways</t>
         </is>
       </c>
       <c r="K456" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L456" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M456" s="18" t="inlineStr">
@@ -29741,12 +29741,12 @@
       </c>
       <c r="E457" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F457" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G457" s="18" t="inlineStr">
@@ -29766,15 +29766,15 @@
       </c>
       <c r="J457" s="18" t="inlineStr">
         <is>
-          <t>Divisional Railway Offices recruit via RRCs and RRBs.</t>
+          <t>Railway Board Vacancy Circulars - covers Divisional Railway Office recruitment</t>
         </is>
       </c>
       <c r="K457" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L457" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M457" s="18" t="inlineStr">
@@ -29805,12 +29805,12 @@
       </c>
       <c r="E458" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F458" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G458" s="18" t="inlineStr">
@@ -29830,15 +29830,15 @@
       </c>
       <c r="J458" s="18" t="inlineStr">
         <is>
-          <t>Production Units (CLW/ICF/DLW/RCF/MCF) recruit via RRBs/RRCs.</t>
+          <t>Railway Board Vacancy Circulars - covers Production Units (CLW/ICF/DLW/RCF/MCF) recruitment</t>
         </is>
       </c>
       <c r="K458" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L458" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M458" s="18" t="inlineStr">
@@ -29889,25 +29889,25 @@
       </c>
       <c r="I459" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J459" s="18" t="inlineStr">
         <is>
-          <t>Railway Recruitment Boards - the primary recruitment agency for railways. Active 2026 recruitment. Site uses rrbapply.gov.in for online applications.</t>
+          <t>RRB centralized application portal - recruitment and application site for Railway Recruitment Boards</t>
         </is>
       </c>
       <c r="K459" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L459" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M459" s="18" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -29933,12 +29933,12 @@
       </c>
       <c r="E460" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="F460" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://indianrailways.gov.in/railwayboard/view_section.jsp?lang=0&amp;id=0,5,373</t>
         </is>
       </c>
       <c r="G460" s="18" t="inlineStr">
@@ -29958,15 +29958,15 @@
       </c>
       <c r="J460" s="18" t="inlineStr">
         <is>
-          <t>Railway Training Institutes subordinate to Railway Board.</t>
+          <t>Railway Board Vacancy Circulars - covers Railway Training Institutes recruitment</t>
         </is>
       </c>
       <c r="K460" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L460" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M460" s="18" t="inlineStr">
@@ -29997,12 +29997,12 @@
       </c>
       <c r="E461" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://gsv.ac.in/careers/</t>
         </is>
       </c>
       <c r="F461" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://gsv.ac.in/careers/</t>
         </is>
       </c>
       <c r="G461" s="18" t="inlineStr">
@@ -30017,20 +30017,20 @@
       </c>
       <c r="I461" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J461" s="18" t="inlineStr">
         <is>
-          <t>NRTI (National Rail &amp; Transportation Institute, now GISMA?). Autonomous body.</t>
+          <t>Gati Shakti Vishwavidyalaya (formerly NRTI) careers page with active job postings</t>
         </is>
       </c>
       <c r="K461" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L461" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M461" s="18" t="inlineStr">
@@ -30061,12 +30061,12 @@
       </c>
       <c r="E462" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://iritm.indianrailways.gov.in/view_section.jsp?lang=0&amp;id=0,4,525</t>
         </is>
       </c>
       <c r="F462" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://iritm.indianrailways.gov.in/view_section.jsp?lang=0&amp;id=0,4,525</t>
         </is>
       </c>
       <c r="G462" s="18" t="inlineStr">
@@ -30086,15 +30086,15 @@
       </c>
       <c r="J462" s="18" t="inlineStr">
         <is>
-          <t>IRITM - Railway Institute of Transport Management.</t>
+          <t>IRITM Vacancies section page</t>
         </is>
       </c>
       <c r="K462" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L462" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M462" s="18" t="inlineStr">
@@ -30125,12 +30125,12 @@
       </c>
       <c r="E463" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://www.ircon.org/hr-career</t>
         </is>
       </c>
       <c r="F463" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://www.ircon.org/hr-career</t>
         </is>
       </c>
       <c r="G463" s="18" t="inlineStr">
@@ -30145,20 +30145,20 @@
       </c>
       <c r="I463" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J463" s="18" t="inlineStr">
         <is>
-          <t>IRCON is a PSU recruiting independently at ircon.org. Policy entry.</t>
+          <t>IRCON International HR Career page with current recruitment openings</t>
         </is>
       </c>
       <c r="K463" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L463" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M463" s="18" t="inlineStr">
@@ -30189,12 +30189,12 @@
       </c>
       <c r="E464" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://rites.com/Career</t>
         </is>
       </c>
       <c r="F464" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://rites.com/Career</t>
         </is>
       </c>
       <c r="G464" s="18" t="inlineStr">
@@ -30209,20 +30209,20 @@
       </c>
       <c r="I464" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J464" s="18" t="inlineStr">
         <is>
-          <t>RITES is a PSU recruiting independently at rites.com. Policy entry.</t>
+          <t>RITES Limited career page with active recruitment and engage portal (recruit.rites.com)</t>
         </is>
       </c>
       <c r="K464" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L464" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M464" s="18" t="inlineStr">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -30253,12 +30253,12 @@
       </c>
       <c r="E465" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://rvnl.org/career</t>
         </is>
       </c>
       <c r="F465" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://rvnl.org/career</t>
         </is>
       </c>
       <c r="G465" s="18" t="inlineStr">
@@ -30278,15 +30278,15 @@
       </c>
       <c r="J465" s="18" t="inlineStr">
         <is>
-          <t>RVNL is a PSU recruiting independently. Policy entry.</t>
+          <t>RVNL career page (CDX confirmed rvnl.org/career active 2017-2022+, vacancy PDFs at /RVNL_cms_v113/uploads/careers/). Site unreachable from sandbox but domain confirmed active via Wayback Dec 2024 snapshot.</t>
         </is>
       </c>
       <c r="K465" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L465" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M465" s="18" t="inlineStr">
@@ -30317,12 +30317,12 @@
       </c>
       <c r="E466" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://www.irctc.com/recruitment.php</t>
         </is>
       </c>
       <c r="F466" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://www.irctc.com/recruitment.php</t>
         </is>
       </c>
       <c r="G466" s="18" t="inlineStr">
@@ -30342,15 +30342,15 @@
       </c>
       <c r="J466" s="18" t="inlineStr">
         <is>
-          <t>IRCTC is a PSU recruiting independently at irctc.com. Policy entry.</t>
+          <t>IRCTC recruitment page (live 200, 12 recruitment keyword matches, meta description: "Explore IRCTC recruitment opportunities"). Canonical: irctc.com/recruitment.php.</t>
         </is>
       </c>
       <c r="K466" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L466" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M466" s="18" t="inlineStr">
@@ -30381,12 +30381,12 @@
       </c>
       <c r="E467" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://www.concorindia.co.in/careers.asp</t>
         </is>
       </c>
       <c r="F467" s="17" t="inlineStr">
         <is>
-          <t>https://indianrailways.gov.in/</t>
+          <t>https://www.concorindia.co.in/careers.asp</t>
         </is>
       </c>
       <c r="G467" s="18" t="inlineStr">
@@ -30406,15 +30406,15 @@
       </c>
       <c r="J467" s="18" t="inlineStr">
         <is>
-          <t>CONCOR is a PSU. Policy entry.</t>
+          <t>CONCOR careers page (live 200, React SPA at /careers.asp). Container Corporation of India recruitment section.</t>
         </is>
       </c>
       <c r="K467" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L467" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M467" s="18" t="inlineStr">
@@ -30957,12 +30957,12 @@
       </c>
       <c r="E476" s="17" t="inlineStr">
         <is>
-          <t>https://nhai.gov.in/</t>
+          <t>https://nhai.gov.in/recruitment-in-nhai.htm</t>
         </is>
       </c>
       <c r="F476" s="17" t="inlineStr">
         <is>
-          <t>https://nhai.gov.in/</t>
+          <t>https://nhai.gov.in/recruitment-in-nhai.htm</t>
         </is>
       </c>
       <c r="G476" s="18" t="inlineStr">
@@ -30982,11 +30982,11 @@
       </c>
       <c r="J476" s="18" t="inlineStr">
         <is>
-          <t>NHAI site verified live. Statutory body under MoRTH. Major recruitment.</t>
+          <t>NHAI recruitment page (Wayback confirmed title "Recruitment in NHAI", has Apply Online links for various posts). Site unreachable from sandbox but confirmed active via CDX Nov 2025 PDF upload.</t>
         </is>
       </c>
       <c r="K476" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L476" s="18" t="inlineStr">
         <is>
@@ -34797,12 +34797,12 @@
       </c>
       <c r="E536" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F536" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G536" s="18" t="inlineStr">
@@ -34822,11 +34822,11 @@
       </c>
       <c r="J536" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Textiles official site (ministryoftextiles.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+          <t>Ministry of Textiles Advertisement/Vacancy page (Wayback Nov 2025 confirmed, title "Advertisement | Ministry of Textiles | GoI", 12 recruitment mentions). Lists vacancy circulars and deputation posts.</t>
         </is>
       </c>
       <c r="K536" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L536" s="18" t="inlineStr">
         <is>
@@ -34861,12 +34861,12 @@
       </c>
       <c r="E537" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F537" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G537" s="18" t="inlineStr">
@@ -34886,11 +34886,11 @@
       </c>
       <c r="J537" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Textiles Secretariat. Site unreachable but confirmed domain.</t>
+          <t>Ministry of Textiles Secretariat uses same Advertisement page for vacancy circulars (Wayback confirmed Nov 2025).</t>
         </is>
       </c>
       <c r="K537" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L537" s="18" t="inlineStr">
         <is>
@@ -34925,12 +34925,12 @@
       </c>
       <c r="E538" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://txcindia.gov.in/html/vacancy%20post%20of%20JC%20.htm</t>
         </is>
       </c>
       <c r="F538" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://txcindia.gov.in/html/vacancy%20post%20of%20JC%20.htm</t>
         </is>
       </c>
       <c r="G538" s="18" t="inlineStr">
@@ -34950,15 +34950,15 @@
       </c>
       <c r="J538" s="18" t="inlineStr">
         <is>
-          <t>Office of Textile Commissioner under MoT.</t>
+          <t>Office of Textile Commissioner vacancy page (live 200, 7 vacancy/recruitment keyword matches). txcindia.gov.in is the official OTC website.</t>
         </is>
       </c>
       <c r="K538" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L538" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M538" s="18" t="inlineStr">
@@ -34989,12 +34989,12 @@
       </c>
       <c r="E539" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F539" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G539" s="18" t="inlineStr">
@@ -35014,15 +35014,15 @@
       </c>
       <c r="J539" s="18" t="inlineStr">
         <is>
-          <t>DC (Handlooms) under MoT.</t>
+          <t>DC (Handlooms) recruitment via Ministry of Textiles Advertisement page. handlooms.nic.in hosts PDF advertisements but no dedicated recruitment landing page found.</t>
         </is>
       </c>
       <c r="K539" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L539" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M539" s="18" t="inlineStr">
@@ -35053,12 +35053,12 @@
       </c>
       <c r="E540" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F540" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G540" s="18" t="inlineStr">
@@ -35078,15 +35078,15 @@
       </c>
       <c r="J540" s="18" t="inlineStr">
         <is>
-          <t>DC (Handicrafts) under MoT.</t>
+          <t>DC (Handicrafts) recruitment via Ministry of Textiles Advertisement page. handicrafts.nic.in has recruitment PDFs but no dedicated landing page.</t>
         </is>
       </c>
       <c r="K540" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L540" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M540" s="18" t="inlineStr">
@@ -35117,12 +35117,12 @@
       </c>
       <c r="E541" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F541" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G541" s="18" t="inlineStr">
@@ -35142,15 +35142,15 @@
       </c>
       <c r="J541" s="18" t="inlineStr">
         <is>
-          <t>DC (Powerloom) under MoT.</t>
+          <t>DC (Powerloom) recruitment via Ministry of Textiles Advertisement page. No separate powerloom recruitment portal found.</t>
         </is>
       </c>
       <c r="K541" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L541" s="18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M541" s="18" t="inlineStr">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -35181,12 +35181,12 @@
       </c>
       <c r="E542" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F542" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G542" s="18" t="inlineStr">
@@ -35206,11 +35206,11 @@
       </c>
       <c r="J542" s="18" t="inlineStr">
         <is>
-          <t>National Jute Board under MoT.</t>
+          <t>National Jute Board under MoT. No independent recruitment domain exists (juteboard.gov.in/njb.gov.in not found). Recruitment handled via Ministry of Textiles advertisement page (Wayback Nov 2025 confirmed vacancy circulars under /advertisement/ path).</t>
         </is>
       </c>
       <c r="K542" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L542" s="18" t="inlineStr">
         <is>
@@ -35245,12 +35245,12 @@
       </c>
       <c r="E543" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://csb.gov.in/job-opportunities/job/</t>
         </is>
       </c>
       <c r="F543" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://csb.gov.in/job-opportunities/job/</t>
         </is>
       </c>
       <c r="G543" s="18" t="inlineStr">
@@ -35270,11 +35270,11 @@
       </c>
       <c r="J543" s="18" t="inlineStr">
         <is>
-          <t>Central Silk Board coordination under MoT.</t>
+          <t>Central Silk Board coordination under MoT. CSB has dedicated job opportunities page (Wayback Jan 2025 confirmed title "CSB - Central Silk Board", 45+ recruitment keyword mentions including walk-in interviews and notifications).</t>
         </is>
       </c>
       <c r="K543" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L543" s="18" t="inlineStr">
         <is>
@@ -35309,12 +35309,12 @@
       </c>
       <c r="E544" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://txcindia.gov.in/html/vacancy%20post%20of%20JC%20.htm</t>
         </is>
       </c>
       <c r="F544" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://txcindia.gov.in/html/vacancy%20post%20of%20JC%20.htm</t>
         </is>
       </c>
       <c r="G544" s="18" t="inlineStr">
@@ -35334,11 +35334,11 @@
       </c>
       <c r="J544" s="18" t="inlineStr">
         <is>
-          <t>Textile Commissionerate Regional/Field Offices.</t>
+          <t>Textile Commissionerate Regional/Field Offices. Office of Textile Commissioner official site (txcindia.gov.in) has vacancy page (live 200, 7 vacancy keyword matches confirmed in batch 13).</t>
         </is>
       </c>
       <c r="K544" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L544" s="18" t="inlineStr">
         <is>
@@ -35373,12 +35373,12 @@
       </c>
       <c r="E545" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F545" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G545" s="18" t="inlineStr">
@@ -35398,11 +35398,11 @@
       </c>
       <c r="J545" s="18" t="inlineStr">
         <is>
-          <t>Handloom/Handicrafts Field Formations.</t>
+          <t>Handloom/Handicrafts Field Formations. No independent recruitment page (handlooms.nic.in has no vacancy section). Recruitment handled via Ministry of Textiles advertisement page.</t>
         </is>
       </c>
       <c r="K545" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L545" s="18" t="inlineStr">
         <is>
@@ -35437,12 +35437,12 @@
       </c>
       <c r="E546" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F546" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G546" s="18" t="inlineStr">
@@ -35462,11 +35462,11 @@
       </c>
       <c r="J546" s="18" t="inlineStr">
         <is>
-          <t>Powerloom Service Centres.</t>
+          <t>Powerloom Service Centres. No independent recruitment domain/page. PSC recruitment handled via Ministry of Textiles advertisement page.</t>
         </is>
       </c>
       <c r="K546" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L546" s="18" t="inlineStr">
         <is>
@@ -35501,12 +35501,12 @@
       </c>
       <c r="E547" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://textilescommittee.nic.in/detail-advertisement-various-technical-and-non-technical-posts-apply-online</t>
         </is>
       </c>
       <c r="F547" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://textilescommittee.nic.in/detail-advertisement-various-technical-and-non-technical-posts-apply-online</t>
         </is>
       </c>
       <c r="G547" s="18" t="inlineStr">
@@ -35526,11 +35526,11 @@
       </c>
       <c r="J547" s="18" t="inlineStr">
         <is>
-          <t>Textiles Committee statutory body.</t>
+          <t>Textiles Committee statutory body. Has dedicated advertisement page (Wayback Jan 2025 confirmed title "Detail advertisement for various Technical and Non-Technical posts (Apply Online)", 11 apply mentions, 11 advertisement mentions).</t>
         </is>
       </c>
       <c r="K547" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L547" s="18" t="inlineStr">
         <is>
@@ -35565,12 +35565,12 @@
       </c>
       <c r="E548" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://csb.gov.in/job-opportunities/job/</t>
         </is>
       </c>
       <c r="F548" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://csb.gov.in/job-opportunities/job/</t>
         </is>
       </c>
       <c r="G548" s="18" t="inlineStr">
@@ -35590,11 +35590,11 @@
       </c>
       <c r="J548" s="18" t="inlineStr">
         <is>
-          <t>Central Silk Board statutory body. Has csb.gov.in site.</t>
+          <t>Central Silk Board statutory body. CSB has dedicated job-opportunities page (Wayback Jan 2025 confirmed, 45+ recruitment keyword mentions including walk-in interviews and job notifications). Has csb.gov.in site.</t>
         </is>
       </c>
       <c r="K548" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L548" s="18" t="inlineStr">
         <is>
@@ -35693,12 +35693,12 @@
       </c>
       <c r="E550" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://careers.nid.edu/</t>
         </is>
       </c>
       <c r="F550" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://careers.nid.edu/</t>
         </is>
       </c>
       <c r="G550" s="18" t="inlineStr">
@@ -35718,11 +35718,11 @@
       </c>
       <c r="J550" s="18" t="inlineStr">
         <is>
-          <t>NID coordination entry. NID recruits independently at nid.edu.</t>
+          <t>NID coordination entry. NID recruits independently at careers.nid.edu (live 200, title "Home Page - NID Career", keywords: career, opening, position, apply; nid.edu/careers redirects here).</t>
         </is>
       </c>
       <c r="K550" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L550" s="18" t="inlineStr">
         <is>
@@ -35757,12 +35757,12 @@
       </c>
       <c r="E551" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F551" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/</t>
+          <t>https://ministryoftextiles.gov.in/advertisement</t>
         </is>
       </c>
       <c r="G551" s="18" t="inlineStr">
@@ -35782,11 +35782,11 @@
       </c>
       <c r="J551" s="18" t="inlineStr">
         <is>
-          <t>IIHTs under MoT.</t>
+          <t>IIHTs under MoT. Individual IIHT campuses (e.g. iihtguwahati.ac.in) have no recruitment section (only tender pages). IIHT recruitment handled via Ministry of Textiles advertisement page.</t>
         </is>
       </c>
       <c r="K551" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L551" s="18" t="inlineStr">
         <is>
@@ -36525,12 +36525,12 @@
       </c>
       <c r="E563" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F563" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G563" s="18" t="inlineStr">
@@ -36550,15 +36550,15 @@
       </c>
       <c r="J563" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Women &amp; Child Development official site (wcd.gov.in). Unreachable from this environment but confirmed as official domain. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>Ministry of Women and Child Development. Career/vacancy page at wcd.gov.in/offerings/career (CDX confirmed active June 2025, Nov 2024 snapshot shows vacancy references including ncpcrvacancies.wcd.gov.in link, 9 career mentions, job postings listed).</t>
         </is>
       </c>
       <c r="K563" s="19" t="n">
-        <v>46182</v>
+        <v>45823</v>
       </c>
       <c r="L563" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M563" s="18" t="inlineStr">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -36589,12 +36589,12 @@
       </c>
       <c r="E564" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F564" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G564" s="18" t="inlineStr">
@@ -36614,15 +36614,15 @@
       </c>
       <c r="J564" s="18" t="inlineStr">
         <is>
-          <t>Ministry of WCD Secretariat. Site unreachable but confirmed domain. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>WCD Secretariat career page. Wayback confirmed Jun 2025 (200, career/vacancy content). Parent ministry career page for all WCD divisions.</t>
         </is>
       </c>
       <c r="K564" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L564" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M564" s="18" t="inlineStr">
@@ -36653,12 +36653,12 @@
       </c>
       <c r="E565" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F565" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G565" s="18" t="inlineStr">
@@ -36678,11 +36678,11 @@
       </c>
       <c r="J565" s="18" t="inlineStr">
         <is>
-          <t>Child Development Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>Child Development Division - uses WCD career page. Wayback confirmed Jun 2025 (200).</t>
         </is>
       </c>
       <c r="K565" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L565" s="18" t="inlineStr">
         <is>
@@ -36717,12 +36717,12 @@
       </c>
       <c r="E566" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F566" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G566" s="18" t="inlineStr">
@@ -36742,11 +36742,11 @@
       </c>
       <c r="J566" s="18" t="inlineStr">
         <is>
-          <t>Women Empowerment Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>Women Empowerment Division - uses WCD career page. Wayback confirmed Jun 2025 (200).</t>
         </is>
       </c>
       <c r="K566" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L566" s="18" t="inlineStr">
         <is>
@@ -36781,12 +36781,12 @@
       </c>
       <c r="E567" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F567" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G567" s="18" t="inlineStr">
@@ -36806,11 +36806,11 @@
       </c>
       <c r="J567" s="18" t="inlineStr">
         <is>
-          <t>Mission Shakti Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>Mission Shakti Division - uses WCD career page. Wayback confirmed Jun 2025 (200).</t>
         </is>
       </c>
       <c r="K567" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L567" s="18" t="inlineStr">
         <is>
@@ -36845,12 +36845,12 @@
       </c>
       <c r="E568" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F568" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G568" s="18" t="inlineStr">
@@ -36870,11 +36870,11 @@
       </c>
       <c r="J568" s="18" t="inlineStr">
         <is>
-          <t>Mission Vatsalya Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>Mission Vatsalya Division - uses WCD career page. Wayback confirmed Jun 2025 (200).</t>
         </is>
       </c>
       <c r="K568" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L568" s="18" t="inlineStr">
         <is>
@@ -36909,12 +36909,12 @@
       </c>
       <c r="E569" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F569" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G569" s="18" t="inlineStr">
@@ -36934,11 +36934,11 @@
       </c>
       <c r="J569" s="18" t="inlineStr">
         <is>
-          <t>Mission POSHAN 2.0 Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>Mission POSHAN 2.0 Division - uses WCD career page. Wayback confirmed Jun 2025 (200).</t>
         </is>
       </c>
       <c r="K569" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L569" s="18" t="inlineStr">
         <is>
@@ -36973,12 +36973,12 @@
       </c>
       <c r="E570" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F570" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G570" s="18" t="inlineStr">
@@ -36998,11 +36998,11 @@
       </c>
       <c r="J570" s="18" t="inlineStr">
         <is>
-          <t>CARA (Central Adoption Resource Authority) under WCD. Has cara.wcd.gov.in. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>CARA (Central Adoption Resource Authority). No dedicated recruitment page on cara.wcd.gov.in; uses parent ministry WCD career page. Wayback confirmed Jun 2025.</t>
         </is>
       </c>
       <c r="K570" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L570" s="18" t="inlineStr">
         <is>
@@ -37037,12 +37037,12 @@
       </c>
       <c r="E571" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://ncpcr.gov.in/public/recruitment</t>
         </is>
       </c>
       <c r="F571" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://ncpcr.gov.in/public/recruitment</t>
         </is>
       </c>
       <c r="G571" s="18" t="inlineStr">
@@ -37062,11 +37062,11 @@
       </c>
       <c r="J571" s="18" t="inlineStr">
         <is>
-          <t>NCPCR under WCD. Has ncpcr.gov.in. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>NCPCR recruitment page. Live 200, title "Recruitment (NCPCR, Govt. of India)". Contains vacancy circulars and deputation posts.</t>
         </is>
       </c>
       <c r="K571" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L571" s="18" t="inlineStr">
         <is>
@@ -37101,12 +37101,12 @@
       </c>
       <c r="E572" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F572" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G572" s="18" t="inlineStr">
@@ -37126,11 +37126,11 @@
       </c>
       <c r="J572" s="18" t="inlineStr">
         <is>
-          <t>Anganwadi/ICDS Field Units subordinate. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>Anganwadi/ICDS Field Units - uses WCD career page. Wayback confirmed Jun 2025 (200). State-level recruitment handled separately.</t>
         </is>
       </c>
       <c r="K572" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L572" s="18" t="inlineStr">
         <is>
@@ -37165,12 +37165,12 @@
       </c>
       <c r="E573" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="F573" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://wcd.gov.in/offerings/career</t>
         </is>
       </c>
       <c r="G573" s="18" t="inlineStr">
@@ -37190,11 +37190,11 @@
       </c>
       <c r="J573" s="18" t="inlineStr">
         <is>
-          <t>State/District Mission Directorates coordination. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>State/District Mission Directorates - uses WCD career page. Wayback confirmed Jun 2025 (200).</t>
         </is>
       </c>
       <c r="K573" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L573" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -37229,12 +37229,12 @@
       </c>
       <c r="E574" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>http://ncw.nic.in/notice</t>
         </is>
       </c>
       <c r="F574" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>http://ncw.nic.in/notice</t>
         </is>
       </c>
       <c r="G574" s="18" t="inlineStr">
@@ -37249,16 +37249,16 @@
       </c>
       <c r="I574" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J574" s="18" t="inlineStr">
         <is>
-          <t>NCW (National Commission for Women). Statutory body. Has ncw.nic.in. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>NCW notice page with vacancy/deputation posts (Wayback Jul 2024, 200)</t>
         </is>
       </c>
       <c r="K574" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L574" s="18" t="inlineStr">
         <is>
@@ -37293,12 +37293,12 @@
       </c>
       <c r="E575" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://www.nipccd.nic.in/recruitment-vacancies</t>
         </is>
       </c>
       <c r="F575" s="17" t="inlineStr">
         <is>
-          <t>https://wcd.gov.in/</t>
+          <t>https://www.nipccd.nic.in/recruitment-vacancies</t>
         </is>
       </c>
       <c r="G575" s="18" t="inlineStr">
@@ -37313,16 +37313,16 @@
       </c>
       <c r="I575" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J575" s="18" t="inlineStr">
         <is>
-          <t>NIPCCD autonomous body under WCD. Has nipccd.nic.in. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
+          <t>NIPCCD recruitment vacancies page (Wayback 2019-2022, 200)</t>
         </is>
       </c>
       <c r="K575" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L575" s="18" t="inlineStr">
         <is>
@@ -37805,12 +37805,12 @@
       </c>
       <c r="E583" s="17" t="inlineStr">
         <is>
-          <t>https://www.saiindia.in/</t>
+          <t>https://saiindia.gov.in/en/recruitment-notices</t>
         </is>
       </c>
       <c r="F583" s="17" t="inlineStr">
         <is>
-          <t>https://www.saiindia.in/</t>
+          <t>https://saiindia.gov.in/en/recruitment-notices</t>
         </is>
       </c>
       <c r="G583" s="18" t="inlineStr">
@@ -37825,20 +37825,20 @@
       </c>
       <c r="I583" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J583" s="18" t="inlineStr">
         <is>
-          <t>SAI site unreachable from environment. Confirmed official domain (saiindia.in or sfrfn). Autonomous body.</t>
+          <t>SAI recruitment notices page (live 200, new domain saiindia.gov.in)</t>
         </is>
       </c>
       <c r="K583" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L583" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M583" s="18" t="inlineStr">
@@ -38061,12 +38061,12 @@
       </c>
       <c r="E587" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://heavyindustries.gov.in/en/job-opportunites</t>
         </is>
       </c>
       <c r="F587" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://heavyindustries.gov.in/en/job-opportunites</t>
         </is>
       </c>
       <c r="G587" s="18" t="inlineStr">
@@ -38081,20 +38081,20 @@
       </c>
       <c r="I587" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J587" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Heavy Industries official site (heavyindustries.gov.in). Unreachable from this environment but confirmed as official domain. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>MHI Job Opportunities page (live 200, official menu link)</t>
         </is>
       </c>
       <c r="K587" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L587" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M587" s="18" t="inlineStr">
@@ -38125,12 +38125,12 @@
       </c>
       <c r="E588" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://heavyindustries.gov.in/en/job-opportunites</t>
         </is>
       </c>
       <c r="F588" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://heavyindustries.gov.in/en/job-opportunites</t>
         </is>
       </c>
       <c r="G588" s="18" t="inlineStr">
@@ -38145,20 +38145,20 @@
       </c>
       <c r="I588" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J588" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Heavy Industries Secretariat. Site unreachable but confirmed domain. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>MHI Job Opportunities page (live 200, official menu link)</t>
         </is>
       </c>
       <c r="K588" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L588" s="18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M588" s="18" t="inlineStr">
@@ -38189,12 +38189,12 @@
       </c>
       <c r="E589" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://heavyindustries.gov.in/en/job-opportunites</t>
         </is>
       </c>
       <c r="F589" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://heavyindustries.gov.in/en/job-opportunites</t>
         </is>
       </c>
       <c r="G589" s="18" t="inlineStr">
@@ -38209,16 +38209,16 @@
       </c>
       <c r="I589" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J589" s="18" t="inlineStr">
         <is>
-          <t>Heavy Engineering Division. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>MHI Job Opportunities page (live 200, official menu link)</t>
         </is>
       </c>
       <c r="K589" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L589" s="18" t="inlineStr">
         <is>
@@ -38253,12 +38253,12 @@
       </c>
       <c r="E590" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://heavyindustries.gov.in/en/job-opportunites</t>
         </is>
       </c>
       <c r="F590" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://heavyindustries.gov.in/en/job-opportunites</t>
         </is>
       </c>
       <c r="G590" s="18" t="inlineStr">
@@ -38273,16 +38273,16 @@
       </c>
       <c r="I590" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J590" s="18" t="inlineStr">
         <is>
-          <t>Automotive Industry Division. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>MHI Job Opportunities page (live 200, official menu link)</t>
         </is>
       </c>
       <c r="K590" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L590" s="18" t="inlineStr">
         <is>
@@ -38317,12 +38317,12 @@
       </c>
       <c r="E591" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://www.araiindia.com/careers</t>
         </is>
       </c>
       <c r="F591" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://www.araiindia.com/careers</t>
         </is>
       </c>
       <c r="G591" s="18" t="inlineStr">
@@ -38337,16 +38337,16 @@
       </c>
       <c r="I591" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J591" s="18" t="inlineStr">
         <is>
-          <t>ARAI autonomous body. Has araiindia.com. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>ARAI careers page (live 301 to MaxHR recruitment portal)</t>
         </is>
       </c>
       <c r="K591" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L591" s="18" t="inlineStr">
         <is>
@@ -38381,12 +38381,12 @@
       </c>
       <c r="E592" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://icat.in/careers/</t>
         </is>
       </c>
       <c r="F592" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://icat.in/careers/</t>
         </is>
       </c>
       <c r="G592" s="18" t="inlineStr">
@@ -38401,16 +38401,16 @@
       </c>
       <c r="I592" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J592" s="18" t="inlineStr">
         <is>
-          <t>ICAT autonomous body. Has icat.in. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>ICAT careers page (live 200, WordPress site)</t>
         </is>
       </c>
       <c r="K592" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L592" s="18" t="inlineStr">
         <is>
@@ -38445,12 +38445,12 @@
       </c>
       <c r="E593" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://cmti.res.in/career/</t>
         </is>
       </c>
       <c r="F593" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://cmti.res.in/career/</t>
         </is>
       </c>
       <c r="G593" s="18" t="inlineStr">
@@ -38465,16 +38465,16 @@
       </c>
       <c r="I593" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J593" s="18" t="inlineStr">
         <is>
-          <t>CMTI autonomous body. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>CMTI career page (live 200, new domain cmti.res.in, redirected from cmti-india.net)</t>
         </is>
       </c>
       <c r="K593" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L593" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -38509,12 +38509,12 @@
       </c>
       <c r="E594" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://www.bhel.com/recruitment</t>
         </is>
       </c>
       <c r="F594" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://www.bhel.com/recruitment</t>
         </is>
       </c>
       <c r="G594" s="18" t="inlineStr">
@@ -38534,11 +38534,11 @@
       </c>
       <c r="J594" s="18" t="inlineStr">
         <is>
-          <t>BHEL is a PSU recruiting independently at bhel.com. Policy entry. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>BHEL dedicated recruitment page with current job openings and career information.</t>
         </is>
       </c>
       <c r="K594" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L594" s="18" t="inlineStr">
         <is>
@@ -38573,12 +38573,12 @@
       </c>
       <c r="E595" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://www.hmtindia.com/careers/</t>
         </is>
       </c>
       <c r="F595" s="17" t="inlineStr">
         <is>
-          <t>https://heavyindustries.gov.in/en/whats-new</t>
+          <t>https://www.hmtindia.com/careers/</t>
         </is>
       </c>
       <c r="G595" s="18" t="inlineStr">
@@ -38598,11 +38598,11 @@
       </c>
       <c r="J595" s="18" t="inlineStr">
         <is>
-          <t>HMT Limited PSU. Policy entry. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
+          <t>HMT Limited careers page. Site behind Cloudflare; URL confirmed via Wayback Machine archive.</t>
         </is>
       </c>
       <c r="K595" s="19" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="L595" s="18" t="inlineStr">
         <is>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42) (1).xlsx
@@ -1592,12 +1592,12 @@
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>https://ccrum.res.in/UserView/index?mid=1752</t>
+          <t>https://ccrum.res.in/recruitment</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
         <is>
-          <t>https://ccrum.res.in/UserView/index?mid=1752</t>
+          <t>https://ccrum.res.in/recruitment</t>
         </is>
       </c>
       <c r="G19" s="18" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>https://ncert.nic.in/CareerGuide.php?ln=hi</t>
+          <t>https://ncert.nic.in/careers</t>
         </is>
       </c>
       <c r="F160" s="17" t="inlineStr">
         <is>
-          <t>https://ncert.nic.in/CareerGuide.php?ln=hi</t>
+          <t>https://ncert.nic.in/careers</t>
         </is>
       </c>
       <c r="G160" s="18" t="inlineStr">
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E169" s="17" t="inlineStr">
         <is>
-          <t>https://ntarecruitment.ntaonline.in/</t>
+          <t>https://nta.ac.in/careers</t>
         </is>
       </c>
       <c r="F169" s="17" t="inlineStr">
         <is>
-          <t>https://ntarecruitment.ntaonline.in/</t>
+          <t>https://nta.ac.in/careers</t>
         </is>
       </c>
       <c r="G169" s="18" t="inlineStr">
@@ -16500,12 +16500,12 @@
       </c>
       <c r="E252" s="17" t="inlineStr">
         <is>
-          <t>https://www.iifpt.edu.in/careers.php</t>
+          <t>http://www.iifpt.edu.in/careers.php</t>
         </is>
       </c>
       <c r="F252" s="17" t="inlineStr">
         <is>
-          <t>https://www.iifpt.edu.in/careers.php</t>
+          <t>http://www.iifpt.edu.in/careers.php</t>
         </is>
       </c>
       <c r="G252" s="18" t="inlineStr">
@@ -24685,12 +24685,12 @@
       </c>
       <c r="E378" s="17" t="inlineStr">
         <is>
-          <t>https://career.nise.res.in/</t>
+          <t>https://nise.res.in/careers</t>
         </is>
       </c>
       <c r="F378" s="17" t="inlineStr">
         <is>
-          <t>https://career.nise.res.in/</t>
+          <t>https://nise.res.in/careers</t>
         </is>
       </c>
       <c r="G378" s="18" t="inlineStr">
@@ -34797,12 +34797,12 @@
       </c>
       <c r="E536" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F536" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G536" s="18" t="inlineStr">
@@ -34861,12 +34861,12 @@
       </c>
       <c r="E537" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F537" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G537" s="18" t="inlineStr">
@@ -34989,12 +34989,12 @@
       </c>
       <c r="E539" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F539" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G539" s="18" t="inlineStr">
@@ -35053,12 +35053,12 @@
       </c>
       <c r="E540" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F540" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G540" s="18" t="inlineStr">
@@ -35117,12 +35117,12 @@
       </c>
       <c r="E541" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F541" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G541" s="18" t="inlineStr">
@@ -35181,12 +35181,12 @@
       </c>
       <c r="E542" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F542" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G542" s="18" t="inlineStr">
@@ -35373,12 +35373,12 @@
       </c>
       <c r="E545" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F545" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G545" s="18" t="inlineStr">
@@ -35437,12 +35437,12 @@
       </c>
       <c r="E546" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F546" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G546" s="18" t="inlineStr">
@@ -35757,12 +35757,12 @@
       </c>
       <c r="E551" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F551" s="17" t="inlineStr">
         <is>
-          <t>https://ministryoftextiles.gov.in/advertisement</t>
+          <t>https://texmin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G551" s="18" t="inlineStr">
